--- a/outputs/glycerol_TEA.xlsx
+++ b/outputs/glycerol_TEA.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,68 +556,130 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Operating hours</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>8000</v>
+          <t>Stranding barrier</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h/yr</t>
+          <t>methanol | quality | unresolved</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEPCI (current)</t>
+          <t>Crude disposal cost (invoiced)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>870.5</v>
+        <v>200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>$/t</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEPCI source</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Chemical Engineering Plant Cost Index, June 2026 preliminary = 870.5 (May 2026 final = 864.0; June 2025 final = 810.4), chemengonline.com, published 2026-08-24. Historical annual values are the conventional published annual averages.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>Client crude netback</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-200</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>$/t (negative)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Discount rate</t>
+          <t>Merchant crude (third-party)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.12</v>
+        <v>400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>$/t</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Operating hours</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CEPCI (current)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CEPCI source</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Chemical Engineering Plant Cost Index, June 2026 preliminary = 870.5 (May 2026 final = 864.0; June 2025 final = 810.4), chemengonline.com, published 2026-08-24. Historical annual values are the conventional published annual averages.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Discount rate</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Discount rate justification</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>12% nominal, applied to a mid-size private biodiesel producer:
   - A chemical major's WACC is typically 7-9%; this client is smaller, privately
@@ -626,65 +688,14 @@
     feedstock supply is itself policy-dependent (RFS/RVO, blender's credit, LCFS),
     so project risk and feedstock risk are CORRELATED rather than independent.
   - 10-12% is the range the brief proposes; 12% is taken as the base and 10% is
-    carried in the sensitivity.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Project life</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>yr</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Construction period</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>yr</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Tax rate</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>fraction</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>MACRS 5-year. IRS asset class 28.0 (Manufacture of Chemicals and Allied Products) carries a 5-year GDS recovery period, so 5-year MACRS is the base. Many TEA texts default to 7-year; that case is run as a check and moves NPV by well under the capex uncertainty band.</t>
+    carried in the sensitivity.
+CAVEAT ON THE NEGATIVE-NETBACK BASIS: the first bullet no longer applies
+uniformly. A large share of every route's value is now AVOIDED CONTRACTUAL COST,
+which carries none of the glycerine spread exposure that justifies 12%. E1's
+case is avoided disposal plus a local feed sale; C1's is still the spread. So the
+cheap route is now also the LOW-RISK route. Applying 12% throughout is
+deliberately conservative rather than correct, and that is stated rather than
+left implicit.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -692,148 +703,206 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Working capital</t>
+          <t>Project life</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.15</v>
+        <v>15</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>fraction of FCI</t>
+          <t>yr</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Construction period</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.045</v>
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>fraction of FCI</t>
+          <t>yr</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Insurance and property tax</t>
+          <t>Tax rate</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>fraction of FCI</t>
+          <t>fraction</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Supervision</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>fraction of labour</t>
-        </is>
-      </c>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MACRS 5-year. IRS asset class 28.0 (Manufacture of Chemicals and Allied Products) carries a 5-year GDS recovery period, so 5-year MACRS is the base. Many TEA texts default to 7-year; that case is run as a check and moves NPV by well under the capex uncertainty band.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Plant overhead</t>
+          <t>Working capital</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>fraction of labour + maintenance</t>
+          <t>fraction of FCI</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shifts per position</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.8</v>
+        <v>0.045</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FTE per position for 24/7 cover</t>
+          <t>fraction of FCI</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Contingency</t>
+          <t>Insurance and property tax</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>fraction of direct cost</t>
+          <t>fraction of FCI</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Owner's cost</t>
+          <t>Supervision</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>fraction of FCI</t>
+          <t>fraction of labour</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Capex accuracy</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>AACE Class 4 (-30% / +50%), factored estimate, CEPCI-escalated</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>Plant overhead</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>fraction of labour + maintenance</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Shifts per position</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FTE per position for 24/7 cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Contingency</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>fraction of direct cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Owner's cost</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>fraction of FCI</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Capex accuracy</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AACE Class 4 (-30% / +50%), factored estimate, CEPCI-escalated</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Feed transfer price convention</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Crude glycerol is charged to every route at its A1 market netback (PRICES['crude_glycerol']). Route A1 therefore has zero margin BY CONSTRUCTION and is the explicit hurdle. A zero-feed-cost sensitivity is reported separately.</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Crude glycerol is charged to every route at its A1 netback (PRICES['crude_glycerol']). That netback is now NEGATIVE, so the charge is a CREDIT: every route that consumes glycerol is credited the disposal cost it avoids. Route A1 (dispose) therefore still has zero margin BY CONSTRUCTION and is still the explicit hurdle - the convention is invariant to the sign of the feed value, only the meaning of the zero changes. A zero-feed-cost sensitivity is reported separately; on this basis it removes the avoided-cost credit and is therefore a DOWNSIDE case rather than an upside one.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -937,16 +1006,16 @@
         <v>313.8633694926773</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7989534311685543</v>
+        <v>6.798953431168553</v>
       </c>
       <c r="J2" t="n">
-        <v>79.89534311685543</v>
+        <v>679.8953431168553</v>
       </c>
       <c r="K2" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.05188871099054526</v>
+        <v>0.2344876467967214</v>
       </c>
     </row>
     <row r="3">
@@ -975,16 +1044,16 @@
         <v>271.1461588661009</v>
       </c>
       <c r="I3" t="n">
-        <v>1.439188306151475</v>
+        <v>7.439188306151477</v>
       </c>
       <c r="J3" t="n">
-        <v>95.94588707676502</v>
+        <v>495.9458870767652</v>
       </c>
       <c r="K3" t="n">
-        <v>-17.41157452759904</v>
+        <v>12.32674731375505</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.02658419322950667</v>
+        <v>0.2011224810598429</v>
       </c>
     </row>
     <row r="4">
@@ -1013,16 +1082,16 @@
         <v>232.1325653775628</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4325229446394</v>
+        <v>8.4325229446394</v>
       </c>
       <c r="J4" t="n">
-        <v>121.62614723197</v>
+        <v>421.62614723197</v>
       </c>
       <c r="K4" t="n">
-        <v>-16.8377221022232</v>
+        <v>12.73657292134165</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005695887537738864</v>
+        <v>0.1911532001496705</v>
       </c>
     </row>
     <row r="5">
@@ -1051,16 +1120,16 @@
         <v>206.0964317831254</v>
       </c>
       <c r="I5" t="n">
-        <v>3.491557020660178</v>
+        <v>9.491557020660181</v>
       </c>
       <c r="J5" t="n">
-        <v>139.6622808264071</v>
+        <v>379.6622808264072</v>
       </c>
       <c r="K5" t="n">
-        <v>-15.4578632970734</v>
+        <v>13.86302138457951</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0309747721474678</v>
+        <v>0.1879375542923738</v>
       </c>
     </row>
     <row r="6">
@@ -1089,16 +1158,16 @@
         <v>187.185230602292</v>
       </c>
       <c r="I6" t="n">
-        <v>4.597204460217218</v>
+        <v>10.59720446021722</v>
       </c>
       <c r="J6" t="n">
-        <v>153.2401486739073</v>
+        <v>353.2401486739073</v>
       </c>
       <c r="K6" t="n">
-        <v>-13.59445609218239</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05145652557333369</v>
+        <v>0.1881007470456229</v>
       </c>
     </row>
     <row r="7">
@@ -1127,16 +1196,16 @@
         <v>172.6684043015476</v>
       </c>
       <c r="I7" t="n">
-        <v>5.738160790779479</v>
+        <v>11.73816079077948</v>
       </c>
       <c r="J7" t="n">
-        <v>163.947451165128</v>
+        <v>335.3760225936994</v>
       </c>
       <c r="K7" t="n">
-        <v>-11.39435687117067</v>
+        <v>17.5418903234022</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06861239956638432</v>
+        <v>0.190113269566758</v>
       </c>
     </row>
     <row r="8">
@@ -1165,16 +1234,16 @@
         <v>161.0818536417881</v>
       </c>
       <c r="I8" t="n">
-        <v>6.907074358709788</v>
+        <v>12.90707435870979</v>
       </c>
       <c r="J8" t="n">
-        <v>172.6768589677447</v>
+        <v>322.6768589677447</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.853763761010164</v>
+        <v>19.89423082895743</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08372047392197191</v>
+        <v>0.1931916383606445</v>
       </c>
     </row>
     <row r="9">
@@ -1203,16 +1272,16 @@
         <v>151.5621589430007</v>
       </c>
       <c r="I9" t="n">
-        <v>8.098844914993942</v>
+        <v>14.09884491499394</v>
       </c>
       <c r="J9" t="n">
-        <v>179.9743314443098</v>
+        <v>313.3076647776431</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.032643759941967</v>
+        <v>22.50649207762766</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09727248292351809</v>
+        <v>0.1969002022205013</v>
       </c>
     </row>
     <row r="10">
@@ -1241,16 +1310,16 @@
         <v>143.563474295672</v>
       </c>
       <c r="I10" t="n">
-        <v>9.309761915693034</v>
+        <v>15.30976191569303</v>
       </c>
       <c r="J10" t="n">
-        <v>186.1952383138607</v>
+        <v>306.1952383138607</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.974964654397198</v>
+        <v>25.33793616125608</v>
       </c>
       <c r="L10" t="n">
-        <v>0.10959928620265</v>
+        <v>0.2009821915305707</v>
       </c>
     </row>
     <row r="11">
@@ -1279,16 +1348,16 @@
         <v>136.7218843091148</v>
       </c>
       <c r="I11" t="n">
-        <v>10.53702555652297</v>
+        <v>16.53702555652297</v>
       </c>
       <c r="J11" t="n">
-        <v>191.5822828458722</v>
+        <v>300.6731919367813</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2295792836583867</v>
+        <v>28.35761469415653</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1207501970927227</v>
+        <v>0.2052796776725785</v>
       </c>
     </row>
     <row r="12">
@@ -1317,16 +1386,16 @@
         <v>130.7843584371468</v>
       </c>
       <c r="I12" t="n">
-        <v>11.77846125034315</v>
+        <v>17.77846125034315</v>
       </c>
       <c r="J12" t="n">
-        <v>196.3076875057191</v>
+        <v>296.3076875057191</v>
       </c>
       <c r="K12" t="n">
-        <v>3.430755143841748</v>
+        <v>31.54134512795264</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1305279120467988</v>
+        <v>0.2096924228052142</v>
       </c>
     </row>
     <row r="13">
@@ -1355,16 +1424,16 @@
         <v>125.5688687966991</v>
       </c>
       <c r="I13" t="n">
-        <v>13.03233984783419</v>
+        <v>19.03233984783418</v>
       </c>
       <c r="J13" t="n">
-        <v>200.4975361205259</v>
+        <v>292.8052284282182</v>
       </c>
       <c r="K13" t="n">
-        <v>6.759204261231328</v>
+        <v>34.8241207674195</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1395773874322288</v>
+        <v>0.2140070798294675</v>
       </c>
     </row>
     <row r="14">
@@ -1393,16 +1462,16 @@
         <v>120.9407220109363</v>
       </c>
       <c r="I14" t="n">
-        <v>14.29725934190175</v>
+        <v>20.29725934190175</v>
       </c>
       <c r="J14" t="n">
-        <v>204.2465620271678</v>
+        <v>289.9608477414536</v>
       </c>
       <c r="K14" t="n">
-        <v>10.2166196228311</v>
+        <v>38.20551682190164</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1480544845642717</v>
+        <v>0.2182464271857918</v>
       </c>
     </row>
     <row r="15">
@@ -1431,16 +1500,16 @@
         <v>116.7978572250145</v>
       </c>
       <c r="I15" t="n">
-        <v>15.57206415383886</v>
+        <v>21.57206415383887</v>
       </c>
       <c r="J15" t="n">
-        <v>207.6275220511847</v>
+        <v>287.6275220511849</v>
       </c>
       <c r="K15" t="n">
-        <v>13.78995938445585</v>
+        <v>41.69655099565069</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1560371302835346</v>
+        <v>0.2224627473594858</v>
       </c>
     </row>
     <row r="16">
@@ -1469,16 +1538,16 @@
         <v>113.0613580909519</v>
       </c>
       <c r="I16" t="n">
-        <v>16.85578836148646</v>
+        <v>22.85578836148646</v>
       </c>
       <c r="J16" t="n">
-        <v>210.6973545185808</v>
+        <v>285.6973545185808</v>
       </c>
       <c r="K16" t="n">
-        <v>17.46827724343063</v>
+        <v>45.28686684259914</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1635879600570447</v>
+        <v>0.2266381418385053</v>
       </c>
     </row>
     <row r="17">
@@ -1507,16 +1576,16 @@
         <v>109.6691276595517</v>
       </c>
       <c r="I17" t="n">
-        <v>18.14761472074838</v>
+        <v>24.14761472074838</v>
       </c>
       <c r="J17" t="n">
-        <v>213.5013496558633</v>
+        <v>284.0895849499809</v>
       </c>
       <c r="K17" t="n">
-        <v>21.24227649377087</v>
+        <v>48.9676689804555</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1707581031551886</v>
+        <v>0.2307608574278175</v>
       </c>
     </row>
     <row r="18">
@@ -1545,16 +1614,16 @@
         <v>106.5715523877306</v>
       </c>
       <c r="I18" t="n">
-        <v>19.44684441996219</v>
+        <v>25.44684441996219</v>
       </c>
       <c r="J18" t="n">
-        <v>216.076049110691</v>
+        <v>282.7427157773577</v>
       </c>
       <c r="K18" t="n">
-        <v>25.1039795152899</v>
+        <v>52.73141026566613</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1775898615235294</v>
+        <v>0.2348233488900537</v>
       </c>
     </row>
   </sheetData>
@@ -1615,7 +1684,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1660.117792808295</v>
+        <v>832.4225842901052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1635,23 +1704,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Crude glycerol feed cost for NPV = 0</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>94.26982122291442</v>
-      </c>
+          <t>Disposal cost for NPV = 0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>$/t crude</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Below this feed cost the route beats simply selling the crude.</t>
+          <t>No sign change in the searched interval - NPV does not reach zero anywhere in the plausible range. Above this disposal cost the route beats continuing to pay the hauler. Coupled to the feed netback inside economics().</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1733,9 @@
           <t>Natural gas price for NPV = 0</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>44.19719993864546</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>$/MMBtu</t>
@@ -1675,11 +1744,7 @@
       <c r="E4" t="n">
         <v>13</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No sign change in the searched interval - NPV does not reach zero anywhere in the plausible range. </t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1693,7 +1758,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024.10835111987</v>
+        <v>1136.256862648631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1713,23 +1778,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Crude glycerol feed cost for NPV = 0</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>56.61447345218875</v>
-      </c>
+          <t>Disposal cost for NPV = 0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>$/t crude</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Below this feed cost the route beats simply selling the crude.</t>
+          <t>No sign change in the searched interval - NPV does not reach zero anywhere in the plausible range. Above this disposal cost the route beats continuing to pay the hauler. Coupled to the feed netback inside economics().</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1807,9 @@
           <t>Natural gas price for NPV = 0</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>40.73343181336431</v>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>$/MMBtu</t>
@@ -1753,11 +1818,7 @@
       <c r="E7" t="n">
         <v>13</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No sign change in the searched interval - NPV does not reach zero anywhere in the plausible range. </t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1771,7 +1832,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>540.5847265309851</v>
+        <v>-115.5115009157071</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1779,7 +1840,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>525</v>
+        <v>-200</v>
       </c>
       <c r="F8" t="inlineStr"/>
     </row>
@@ -1791,11 +1852,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Crude glycerol feed cost for NPV = 0</t>
+          <t>Disposal cost for NPV = 0</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>385.7477675874142</v>
+        <v>277.2647324125858</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1803,11 +1864,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Below this feed cost the route beats simply selling the crude.</t>
+          <t>Above this disposal cost the route beats continuing to pay the hauler. Coupled to the feed netback inside economics().</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1910,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1373.905768271237</v>
+        <v>1098.007365431841</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1869,23 +1930,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Crude glycerol feed cost for NPV = 0</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>307.6320673002723</v>
-      </c>
+          <t>Disposal cost for NPV = 0</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>$/t crude</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Below this feed cost the route beats simply selling the crude.</t>
+          <t>No sign change in the searched interval - NPV does not reach zero anywhere in the plausible range. Above this disposal cost the route beats continuing to pay the hauler. Coupled to the feed netback inside economics().</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1960,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.743002660386311</v>
+        <v>24.35536652949306</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1924,9 +1983,7 @@
           <t>MINIMUM ECONOMIC SCALE (NPV = 0)</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>54645.15106828487</v>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>t/yr crude glycerol fed</t>
@@ -1937,7 +1994,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>The client has 10,000 t/yr of its own crude. It must source a further 44,645 t/yr from third parties before a purification plant clears a 12% hurdle.</t>
+          <t>No sign change between 10,000 t/yr (NPV $14.06M) and 200,000 t/yr (NPV $148.52M). Minimum economic scale does not exist on this basis: the flowsheet does not cross zero from below.</t>
         </is>
       </c>
     </row>
@@ -1952,7 +2009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2043,27 +2100,27 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-73.54085557612865</v>
+        <v>-37.18071291054898</v>
       </c>
       <c r="I2" t="n">
-        <v>-13.59445609218239</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="J2" t="n">
-        <v>88.64776117925734</v>
+        <v>115.6479739767793</v>
       </c>
       <c r="K2" t="n">
-        <v>162.188616755386</v>
+        <v>152.8286868873283</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Crude glycerol feed cost / netback</t>
+          <t>Merchant crude (third-party purchase)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>crude_glycerol</t>
+          <t>merchant_crude_glycerol</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2086,16 +2143,16 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>18.00978281073305</v>
+        <v>35.89013050471544</v>
       </c>
       <c r="I3" t="n">
-        <v>-13.59445609218239</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="J3" t="n">
-        <v>-51.12900249724428</v>
+        <v>-6.513811277255267</v>
       </c>
       <c r="K3" t="n">
-        <v>69.13878530797733</v>
+        <v>42.4039417819707</v>
       </c>
     </row>
     <row r="4">
@@ -2129,16 +2186,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.05741473206546</v>
+        <v>29.56253408445967</v>
       </c>
       <c r="I4" t="n">
-        <v>-13.59445609218239</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="J4" t="n">
-        <v>-40.92507011884863</v>
+        <v>-9.623498963271903</v>
       </c>
       <c r="K4" t="n">
-        <v>42.98248485091409</v>
+        <v>39.18603304773157</v>
       </c>
     </row>
     <row r="5">
@@ -2172,16 +2229,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-7.260242382626699</v>
+        <v>21.36587935091706</v>
       </c>
       <c r="I5" t="n">
-        <v>-13.59445609218239</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="J5" t="n">
-        <v>-35.97845358648449</v>
+        <v>-4.362881155299353</v>
       </c>
       <c r="K5" t="n">
-        <v>28.71821120385779</v>
+        <v>25.72876050621641</v>
       </c>
     </row>
     <row r="6">
@@ -2215,16 +2272,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-6.233432187281505</v>
+        <v>22.27949038264008</v>
       </c>
       <c r="I6" t="n">
-        <v>-13.59445609218239</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="J6" t="n">
-        <v>-18.93543715389454</v>
+        <v>10.73182601655775</v>
       </c>
       <c r="K6" t="n">
-        <v>12.70200496661304</v>
+        <v>11.54766436608232</v>
       </c>
     </row>
     <row r="7">
@@ -2258,16 +2315,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-15.55156998829705</v>
+        <v>13.70244072734874</v>
       </c>
       <c r="I7" t="n">
-        <v>-13.59445609218239</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.034635295372027</v>
+        <v>25.12564066624471</v>
       </c>
       <c r="K7" t="n">
-        <v>12.51693469292502</v>
+        <v>11.42319993889597</v>
       </c>
     </row>
     <row r="8">
@@ -2301,16 +2358,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-20.28780476706903</v>
+        <v>9.544615369834831</v>
       </c>
       <c r="I8" t="n">
-        <v>-13.59445609218239</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="J8" t="n">
-        <v>-13.59445609218239</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="K8" t="n">
-        <v>6.693348674886644</v>
+        <v>5.960416940245023</v>
       </c>
     </row>
     <row r="9">
@@ -2344,16 +2401,16 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-11.45487032260471</v>
+        <v>17.4870322509303</v>
       </c>
       <c r="I9" t="n">
-        <v>-13.59445609218239</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="J9" t="n">
-        <v>-18.01365924806048</v>
+        <v>11.54103242837897</v>
       </c>
       <c r="K9" t="n">
-        <v>6.558788925455768</v>
+        <v>5.945999822551331</v>
       </c>
     </row>
     <row r="10">
@@ -2387,170 +2444,170 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-15.23311960649411</v>
+        <v>13.98706045093786</v>
       </c>
       <c r="I10" t="n">
-        <v>-13.59445609218239</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="J10" t="n">
-        <v>-12.36545845644862</v>
+        <v>16.64351120443634</v>
       </c>
       <c r="K10" t="n">
-        <v>2.86766115004549</v>
+        <v>2.656450753498487</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Split soap fatty acid (acid oil) credit</t>
+          <t>Crude glycerol disposal cost (client invoice)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>acid_oil_ffa</t>
+          <t>crude_disposal_cost</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>600</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="E11" t="n">
-        <v>1200</v>
+        <v>220</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>$/t</t>
+          <t>$/t crude (a COST, entered positive)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>sourced</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-14.16448460086154</v>
+        <v>14.56801264394282</v>
       </c>
       <c r="I11" t="n">
-        <v>-13.59445609218239</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="J11" t="n">
-        <v>-13.02442758350323</v>
+        <v>16.44205197621688</v>
       </c>
       <c r="K11" t="n">
-        <v>1.140057017358314</v>
+        <v>1.874039332274059</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sulphuric acid</t>
+          <t>Split soap fatty acid (acid oil) credit</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sulfuric_acid</t>
+          <t>acid_oil_ffa</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="D12" t="n">
-        <v>875</v>
+        <v>900</v>
       </c>
       <c r="E12" t="n">
-        <v>950</v>
+        <v>1200</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>$/t (93%, delivered)</t>
+          <t>$/t</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>sourced</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-12.79881113826544</v>
+        <v>14.97698782289478</v>
       </c>
       <c r="I12" t="n">
-        <v>-13.59445609218239</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="J12" t="n">
-        <v>-13.69823586878026</v>
+        <v>16.03307679726494</v>
       </c>
       <c r="K12" t="n">
-        <v>0.899424730514817</v>
+        <v>1.056088974370161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Activated carbon</t>
+          <t>Sulphuric acid</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>activated_carbon</t>
+          <t>sulfuric_acid</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="D13" t="n">
-        <v>1800</v>
+        <v>875</v>
       </c>
       <c r="E13" t="n">
-        <v>2500</v>
+        <v>950</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>$/t</t>
+          <t>$/t (93%, delivered)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>sourced</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-13.14544741535656</v>
+        <v>16.24207602855281</v>
       </c>
       <c r="I13" t="n">
-        <v>-13.59445609218239</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="J13" t="n">
-        <v>-13.90876216596048</v>
+        <v>15.40889617288774</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7633147506039236</v>
+        <v>0.8331798556650728</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Salt cake and residue disposal</t>
+          <t>Activated carbon</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>solid_waste_disposal</t>
+          <t>activated_carbon</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>800</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>1800</v>
       </c>
       <c r="E14" t="n">
-        <v>110</v>
+        <v>2500</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>$/t (a COST, entered positive)</t>
+          <t>$/t</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2559,102 +2616,188 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>-13.30289731562931</v>
+        <v>15.92097037788903</v>
       </c>
       <c r="I14" t="n">
-        <v>-13.59445609218239</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="J14" t="n">
-        <v>-13.9443266240461</v>
+        <v>15.21387566261343</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6414293084167968</v>
+        <v>0.707094715275595</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Electricity</t>
+          <t>Salt cake and residue disposal</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>solid_waste_disposal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.08599999999999999</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>0.098</v>
+        <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>0.128</v>
+        <v>110</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>$/kWh</t>
+          <t>$/t (a COST, entered positive)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>sourced</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-13.51526445267802</v>
+        <v>15.7751170555008</v>
       </c>
       <c r="I15" t="n">
-        <v>-13.59445609218239</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.79243519094332</v>
+        <v>15.18093061557473</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2771707382653001</v>
+        <v>0.5941864399260637</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>electricity</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>$/kWh</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>15.57839128780596</v>
+      </c>
+      <c r="I16" t="n">
+        <v>15.50503231007985</v>
+      </c>
+      <c r="J16" t="n">
+        <v>15.32163486576463</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2567564220413324</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Caustic soda</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>caustic_soda</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C17" t="n">
         <v>460</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D17" t="n">
         <v>740</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E17" t="n">
         <v>900</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>$/t (100% NaOH dry basis)</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>sourced</t>
         </is>
       </c>
-      <c r="H16" t="n">
-        <v>-13.54731018111568</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-13.59445609218239</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-13.62139661279194</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.07408643167625367</v>
+      <c r="H17" t="n">
+        <v>15.54870580719982</v>
+      </c>
+      <c r="I17" t="n">
+        <v>15.50503231007985</v>
+      </c>
+      <c r="J17" t="n">
+        <v>15.48007602601131</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.06862978118851036</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Feed-grade / de-methanolised product price</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>feed_grade_glycerin</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>-220</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E18" t="n">
+        <v>683</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>$/t (80-88% basis, low methanol) - STRANDED on this scenario</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>15.50503231007985</v>
+      </c>
+      <c r="I18" t="n">
+        <v>15.50503231007985</v>
+      </c>
+      <c r="J18" t="n">
+        <v>15.50503231007985</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2668,7 +2811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2759,84 +2902,84 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-36.01589690869292</v>
+        <v>-2.197807977483519</v>
       </c>
       <c r="I2" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="J2" t="n">
-        <v>20.3701168333845</v>
+        <v>47.37032963090647</v>
       </c>
       <c r="K2" t="n">
-        <v>56.38601374207742</v>
+        <v>49.56813760838999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Crude glycerol feed cost / netback</t>
+          <t>Capex accuracy (AACE Class 4, -30%/+50%)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>crude_glycerol</t>
+          <t>capex_multiplier</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>176</v>
+        <v>0.7</v>
       </c>
       <c r="D3" t="n">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>630</v>
+        <v>1.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>$/t crude (80% basis)</t>
+          <t>multiplier on ISBL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>sourced</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-4.002105401574092</v>
+        <v>21.21966245819424</v>
       </c>
       <c r="I3" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="J3" t="n">
-        <v>-28.54527921573146</v>
+        <v>1.550256131438328</v>
       </c>
       <c r="K3" t="n">
-        <v>24.54317381415737</v>
+        <v>19.66940632675591</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Capex accuracy (AACE Class 4, -30%/+50%)</t>
+          <t>Freight, outbound product and inbound third-party crude</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>capex_multiplier</t>
+          <t>freight_out</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7</v>
+        <v>50</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5</v>
+        <v>180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>multiplier on ISBL</t>
+          <t>$/t product</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2845,41 +2988,41 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-6.903354355921005</v>
+        <v>15.04295766236833</v>
       </c>
       <c r="I4" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="J4" t="n">
-        <v>-29.79193358827482</v>
+        <v>10.7954898453288</v>
       </c>
       <c r="K4" t="n">
-        <v>22.88857923235381</v>
+        <v>4.247467817039529</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Freight, outbound product and inbound third-party crude</t>
+          <t>Burdened labour rate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>freight_out</t>
+          <t>operator_burdened</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>85000</v>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>105000</v>
       </c>
       <c r="E5" t="n">
-        <v>180</v>
+        <v>145000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>$/t product</t>
+          <t>$/operator-year, fully burdened</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2888,127 +3031,127 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-14.25900072284457</v>
+        <v>15.36033905822745</v>
       </c>
       <c r="I5" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="J5" t="n">
-        <v>-19.39916103475917</v>
+        <v>11.47230841538429</v>
       </c>
       <c r="K5" t="n">
-        <v>5.140160311914593</v>
+        <v>3.888030642843165</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Burdened labour rate</t>
+          <t>Natural gas (New York industrial)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>operator_burdened</t>
+          <t>natural_gas</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>85000</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>105000</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>145000</v>
+        <v>16.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>$/operator-year, fully burdened</t>
+          <t>$/MMBtu</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>sourced</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-13.87430440300195</v>
+        <v>16.24750176619341</v>
       </c>
       <c r="I6" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="J6" t="n">
-        <v>-18.58696588616301</v>
+        <v>12.53610779837348</v>
       </c>
       <c r="K6" t="n">
-        <v>4.712661483161066</v>
+        <v>3.711393967819933</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Natural gas (New York industrial)</t>
+          <t>Methanol credit</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>natural_gas</t>
+          <t>methanol</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>450</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>600</v>
       </c>
       <c r="E7" t="n">
-        <v>16.5</v>
+        <v>1414</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>$/MMBtu</t>
+          <t>$/t</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>sourced</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-12.82064445825182</v>
+        <v>13.48719929539936</v>
       </c>
       <c r="I7" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="J7" t="n">
-        <v>-17.29754025181214</v>
+        <v>17.19621852739496</v>
       </c>
       <c r="K7" t="n">
-        <v>4.47689579356032</v>
+        <v>3.709019231995599</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Methanol credit</t>
+          <t>Glycerol recovery -5 percentage points</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>methanol</t>
+          <t>glycerol_conversion</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>450</v>
+        <v>0.8565200000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>600</v>
+        <v>0.9016000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>1414</v>
+        <v>0.9016000000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>$/t</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3017,59 +3160,59 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-16.14472725296235</v>
+        <v>12.15600264802361</v>
       </c>
       <c r="I8" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="J8" t="n">
-        <v>-11.6955050762117</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="K8" t="n">
-        <v>4.449222176750647</v>
+        <v>1.908326195922781</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Glycerol recovery -5 percentage points</t>
+          <t>Crude glycerol disposal cost (client invoice)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>glycerol_conversion</t>
+          <t>crude_disposal_cost</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8565200000000001</v>
+        <v>180</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9016000000000001</v>
+        <v>200</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9016000000000001</v>
+        <v>220</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>$/t crude (a COST, entered positive)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>estimate</t>
+          <t>sourced</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-17.7582637044172</v>
+        <v>13.16432175069566</v>
       </c>
       <c r="I9" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="J9" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.96433593719713</v>
       </c>
       <c r="K9" t="n">
-        <v>2.313072140361566</v>
+        <v>1.800014186501466</v>
       </c>
     </row>
     <row r="10">
@@ -3103,16 +3246,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-16.03427424945076</v>
+        <v>13.57832501359099</v>
       </c>
       <c r="I10" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="J10" t="n">
-        <v>-15.00337955000929</v>
+        <v>14.42883171671294</v>
       </c>
       <c r="K10" t="n">
-        <v>1.030894699441481</v>
+        <v>0.8505067031219415</v>
       </c>
     </row>
     <row r="11">
@@ -3146,16 +3289,16 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-15.6501109521495</v>
+        <v>13.89526665624875</v>
       </c>
       <c r="I11" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.24027217596177</v>
+        <v>14.23339103164403</v>
       </c>
       <c r="K11" t="n">
-        <v>0.409838776187731</v>
+        <v>0.3381243753952757</v>
       </c>
     </row>
     <row r="12">
@@ -3189,16 +3332,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-15.15916538358542</v>
+        <v>14.30030559684859</v>
       </c>
       <c r="I12" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="J12" t="n">
-        <v>-15.48249932672567</v>
+        <v>14.03354926748089</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3233339431402497</v>
+        <v>0.2667563293677028</v>
       </c>
     </row>
     <row r="13">
@@ -3232,16 +3375,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-15.28377756124165</v>
+        <v>14.19749830484808</v>
       </c>
       <c r="I13" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="J13" t="n">
-        <v>-15.55818136602542</v>
+        <v>13.97111022131521</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2744038047837727</v>
+        <v>0.2263880835328717</v>
       </c>
     </row>
     <row r="14">
@@ -3275,16 +3418,16 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>-15.34037918156078</v>
+        <v>14.15080094815875</v>
       </c>
       <c r="I14" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="J14" t="n">
-        <v>-15.57096642304947</v>
+        <v>13.96056231889158</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2305872414886951</v>
+        <v>0.190238629267171</v>
       </c>
     </row>
     <row r="15">
@@ -3318,16 +3461,16 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-15.41672298386657</v>
+        <v>14.08781593558852</v>
       </c>
       <c r="I15" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="J15" t="n">
-        <v>-15.51636301452829</v>
+        <v>14.00561111484108</v>
       </c>
       <c r="K15" t="n">
-        <v>0.09964003066172637</v>
+        <v>0.08220482074743882</v>
       </c>
     </row>
     <row r="16">
@@ -3361,16 +3504,102 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-15.42824309376016</v>
+        <v>14.07831163734107</v>
       </c>
       <c r="I16" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="J16" t="n">
-        <v>-15.45487640422447</v>
+        <v>14.05633867629229</v>
       </c>
       <c r="K16" t="n">
-        <v>0.02663331046430953</v>
+        <v>0.02197296104878187</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Feed-grade / de-methanolised product price</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>feed_grade_glycerin</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>-220</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-200</v>
+      </c>
+      <c r="E17" t="n">
+        <v>683</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>$/t (80-88% basis, low methanol) - STRANDED on this scenario</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>14.06432884394639</v>
+      </c>
+      <c r="I17" t="n">
+        <v>14.06432884394639</v>
+      </c>
+      <c r="J17" t="n">
+        <v>14.06432884394639</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Merchant crude (third-party purchase)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>merchant_crude_glycerol</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>176</v>
+      </c>
+      <c r="D18" t="n">
+        <v>400</v>
+      </c>
+      <c r="E18" t="n">
+        <v>630</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>$/t crude (80% basis)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>14.06432884394639</v>
+      </c>
+      <c r="I18" t="n">
+        <v>14.06432884394639</v>
+      </c>
+      <c r="J18" t="n">
+        <v>14.06432884394639</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3436,7 +3665,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -3461,19 +3690,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>525</v>
+        <v>-200</v>
       </c>
       <c r="D3" t="n">
-        <v>46.54439288595211</v>
+        <v>-16.46810711404788</v>
       </c>
       <c r="E3" t="n">
         <v>3.505294610902948</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7180082959550149</v>
+        <v>-4.19335030214898</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07781002259152592</v>
+        <v>-0.3867773236909647</v>
       </c>
     </row>
     <row r="4">
@@ -3491,16 +3720,16 @@
         <v>1250</v>
       </c>
       <c r="D4" t="n">
-        <v>79.89534311685543</v>
+        <v>679.8953431168553</v>
       </c>
       <c r="E4" t="n">
         <v>21.74738526912969</v>
       </c>
       <c r="F4" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.05188871099054526</v>
+        <v>0.2344876467967214</v>
       </c>
     </row>
     <row r="5">
@@ -3518,16 +3747,16 @@
         <v>1530</v>
       </c>
       <c r="D5" t="n">
-        <v>175.1191023883594</v>
+        <v>775.1191023883595</v>
       </c>
       <c r="E5" t="n">
         <v>25.96901970905098</v>
       </c>
       <c r="F5" t="n">
-        <v>-17.01480446510902</v>
+        <v>12.75053836650466</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.01881335668910433</v>
+        <v>0.2040157472514001</v>
       </c>
     </row>
   </sheetData>
@@ -3557,12 +3786,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>NPV, feed charged at market ($M)</t>
+          <t>NPV, feed charged at netback ($M)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>NPV, feed free ($M)</t>
+          <t>NPV, avoided-disposal credit removed ($M)</t>
         </is>
       </c>
     </row>
@@ -3574,14 +3803,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sell crude glycerol as-is to a merchant refiner</t>
+          <t>Continue paying for disposal (do nothing)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>18.00014186501464</v>
+        <v>-12.16225801690179</v>
       </c>
     </row>
     <row r="3">
@@ -3596,7 +3825,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-25.18249474412187</v>
+        <v>7.644371802708527</v>
       </c>
       <c r="D3" t="n">
         <v>-1.707981470050718</v>
@@ -3614,7 +3843,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-15.44519156405563</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="D4" t="n">
         <v>4.821542152759098</v>
@@ -3632,7 +3861,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-17.01480446510902</v>
+        <v>12.75053836650466</v>
       </c>
       <c r="D5" t="n">
         <v>3.233227631813917</v>
@@ -3650,10 +3879,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-13.64561311501431</v>
+        <v>-9.537127233266444</v>
       </c>
       <c r="D6" t="n">
-        <v>7.902388159904056</v>
+        <v>-21.69938525016823</v>
       </c>
     </row>
     <row r="7">
@@ -3668,7 +3897,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-58.35297999721605</v>
+        <v>-22.53350967005572</v>
       </c>
       <c r="D7" t="n">
         <v>-34.02846396341247</v>
@@ -3686,10 +3915,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.7180082959550149</v>
+        <v>-4.19335030214898</v>
       </c>
       <c r="D8" t="n">
-        <v>17.43011798851957</v>
+        <v>-16.35560831905077</v>
       </c>
     </row>
     <row r="9">
@@ -3704,10 +3933,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-2.029120721894851</v>
+        <v>-5.860992138344971</v>
       </c>
       <c r="D9" t="n">
-        <v>16.49859253081245</v>
+        <v>-18.02325015524675</v>
       </c>
     </row>
     <row r="10">
@@ -3722,7 +3951,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-13.59445609218239</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="D10" t="n">
         <v>6.134835648709558</v>
@@ -3740,10 +3969,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-6.826479162808219</v>
+        <v>-3.706859981472909</v>
       </c>
       <c r="D11" t="n">
-        <v>12.64601778345864</v>
+        <v>-15.86911799837469</v>
       </c>
     </row>
   </sheetData>
@@ -3794,16 +4023,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4708333333333333</v>
+        <v>0.7785</v>
       </c>
       <c r="C2" t="n">
-        <v>-52.09268370667478</v>
+        <v>-15.58512267099246</v>
       </c>
       <c r="D2" t="n">
-        <v>-3.113836795444342</v>
+        <v>25.11084835079634</v>
       </c>
       <c r="E2" t="n">
-        <v>48.71497060357269</v>
+        <v>74.72239426892396</v>
       </c>
     </row>
     <row r="3">
@@ -3813,16 +4042,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.221</v>
+        <v>0.9565</v>
       </c>
       <c r="C3" t="n">
-        <v>-29.33817894948589</v>
+        <v>4.047933514351017</v>
       </c>
       <c r="D3" t="n">
-        <v>-11.67113053972259</v>
+        <v>17.29055998710017</v>
       </c>
       <c r="E3" t="n">
-        <v>7.13769658673553</v>
+        <v>33.49978894367108</v>
       </c>
     </row>
   </sheetData>
@@ -3836,7 +4065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4008,21 +4237,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>feed_grade_glycerin</t>
+          <t>crude_disposal_cost_downside</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>525</v>
+        <v>400</v>
       </c>
       <c r="C5" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="D5" t="n">
-        <v>683</v>
+        <v>600</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>$/t (80-88% basis, low methanol)</t>
+          <t>$/t crude (a COST, entered positive)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4032,17 +4261,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Argus kosher crude 80% fob US Midwest 24-27 c/lb (2026-04-16); Fastmarkets EN-GLY-0004 kosher crude 80% fob US plant 26-31 c/lb (2026-07-28 corrected assessment)</t>
+          <t>Engineering estimate: doubling of the current invoiced rate</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PARTLY INFERRED. The kosher-crude assessment is the closest traded proxy for a clean, low-methanol, consistent-spec crude sold into feed/food channels, but the kosher premium is a FEEDSTOCK-ORIGIN premium, not a methanol-spec premium. The true feed-grade premium for de-methanolised material is not separately assessed. Treat the premium over plain crude as the key uncertainty in route E1.</t>
+          <t>Downside bound carried by route A2. Reached if the current hauler exits, the accepting facility re-profiles the waste, or a solidification or COD-surcharge requirement is imposed. Bounds the downside the way the old A2 (disposal at a positive crude market) used to; on this basis disposal IS the baseline, so the only meaningful downside is that it gets dearer.</t>
         </is>
       </c>
     </row>
@@ -4336,21 +4565,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>solid_waste_disposal</t>
+          <t>second_cut_glycerine</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>-220</v>
       </c>
       <c r="D13" t="n">
-        <v>110</v>
+        <v>630</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>$/t (a COST, entered positive)</t>
+          <t>$/t (85-90% glycerine)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4360,38 +4589,38 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>New York landfill tipping fees, non-hazardous industrial solid waste: DANC Rodman $50.00/short ton (CY2026); Fulton County $68.00 in-county / $77.00 out-of-county (eff. 2026-01-01); Ulster County $150.00 (eff. 2026-01-01). Converted at 1.1023 short ton/t</t>
+          <t>Priced against merchant_crude_glycerol (Argus US Midwest crude 80% fob) as the nearest traded analogue</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TWO MATERIAL CAVEATS. (1) Seneca Meadows, Waterloo NY - the nearest large landfill to a Finger Lakes site - prices industrial waste by WASTE PROFILE and does not publish a rate; its posted MSW rate is $100/ton. (2) Seneca Meadows prohibits free liquids above 20%, so a wet, soluble salt cake may require solidification at unquantified extra cost, or be refused. A site-specific quote against an actual salt-cake analysis is a Stage 2 action.</t>
+          <t>The 3% second cut off the Lurgi yield block. Its own key because it is NOT the client's stranded crude: it is salt-free, methanol-free and 85-90% pure, so it is assumed saleable at the merchant crude assessment even while the raw 80% crude is not. The low bound carries the case where it is stranded too and becomes a disposal liability at the same rate as the feed. Immaterial either way: ~276 t/yr, under $0.2M of swing.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>wastewater</t>
+          <t>solid_waste_disposal</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.5</v>
+        <v>80</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>$/m3</t>
+          <t>$/t (a COST, entered positive)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4401,79 +4630,79 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Engineering estimate - industrial effluent with high COD</t>
+          <t>New York landfill tipping fees, non-hazardous industrial solid waste: DANC Rodman $50.00/short ton (CY2026); Fulton County $68.00 in-county / $77.00 out-of-county (eff. 2026-01-01); Ulster County $150.00 (eff. 2026-01-01). Converted at 1.1023 short ton/t</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Glycerol-bearing effluent is high-COD and surcharged by POTWs.</t>
+          <t>TWO MATERIAL CAVEATS. (1) Seneca Meadows, Waterloo NY - the nearest large landfill to a Finger Lakes site - prices industrial waste by WASTE PROFILE and does not publish a rate; its posted MSW rate is $100/ton. (2) Seneca Meadows prohibits free liquids above 20%, so a wet, soluble salt cake may require solidification at unquantified extra cost, or be refused. A site-specific quote against an actual salt-cake analysis is a Stage 2 action.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dha</t>
+          <t>wastewater</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50000</v>
+        <v>3.5</v>
       </c>
       <c r="C15" t="n">
-        <v>20000</v>
+        <v>1.5</v>
       </c>
       <c r="D15" t="n">
-        <v>150000</v>
+        <v>8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>$/t</t>
+          <t>$/m3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>estimate</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>$150/kg reported 2015, cited in Ciriminna et al., ChemistryOpen 2018 (PMC5838383), which itself warns that 'publicly available prices for DHA differ greatly'; current Chinese supplier list prices $20-50/kg (2025-26)</t>
+          <t>Engineering estimate - industrial effluent with high COD</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>An 11-year-old academic citation at $150/kg against current Chinese bulk offers near $35/kg is a 4x discrepancy that cannot be resolved from public data. Immaterial - the route fails on market volume, not price.</t>
+          <t>Glycerol-bearing effluent is high-COD and surcharged by POTWs.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>propylene_glycol</t>
+          <t>demethanolised_crude</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2000</v>
+        <v>-200</v>
       </c>
       <c r="C16" t="n">
-        <v>1600</v>
+        <v>-220</v>
       </c>
       <c r="D16" t="n">
-        <v>2800</v>
+        <v>630</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>$/t</t>
+          <t>$/t crude (80% basis) - STRANDED on this scenario</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4483,34 +4712,34 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>IndexBox US Propylene Glycol USP market report, contract range $1.20-1.80/lb USP and $0.85-1.25/lb industrial grade (2026)</t>
+          <t>Stranded: valued at the disposal netback. Upside bound is the Argus US Midwest crude 80% fob high</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LOW CONFIDENCE. IndexBox is a market-report aggregator, not a price reporting agency, and its own USP and world-spot figures are mutually inconsistent once units are reconciled. Range is wide on purpose. Immaterial to the conclusion: D1 fails by $50M+.</t>
+          <t>Route F1's product. SET BY STRANDING_BARRIER = 'unresolved'. Stripping methanol is assumed NOT to restore market access, so the de-methanolised material remains stranded and is valued at the disposal netback. The HIGH bound carries the case where methanol was the barrier after all. Flip STRANDING_BARRIER to 'methanol' to price that case.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>solketal</t>
+          <t>dha</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3000</v>
+        <v>50000</v>
       </c>
       <c r="C17" t="n">
-        <v>2400</v>
+        <v>20000</v>
       </c>
       <c r="D17" t="n">
-        <v>6200</v>
+        <v>150000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -4524,7 +4753,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>~$3,000/t cited in Sustainable Chemistry 2021, 2(2), 17 (10.3390/suschem2020017); RMB 45,000/t (97%, China, Apr 2025) per Valuates/QYResearch = ~$6,200/t</t>
+          <t>$150/kg reported 2015, cited in Ciriminna et al., ChemistryOpen 2018 (PMC5838383), which itself warns that 'publicly available prices for DHA differ greatly'; current Chinese supplier list prices $20-50/kg (2025-26)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4532,26 +4761,30 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>An 11-year-old academic citation at $150/kg against current Chinese bulk offers near $35/kg is a 4x discrepancy that cannot be resolved from public data. Immaterial - the route fails on market volume, not price.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>triacetin</t>
+          <t>feed_grade_glycerin</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1300</v>
+        <v>-200</v>
       </c>
       <c r="C18" t="n">
-        <v>1200</v>
+        <v>-220</v>
       </c>
       <c r="D18" t="n">
-        <v>1400</v>
+        <v>683</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>$/t</t>
+          <t>$/t (80-88% basis, low methanol) - STRANDED on this scenario</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4561,34 +4794,34 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ChemAnalyst CFR Mexico $1,400/t (Feb 2026); Chemball fob Shanghai ~$1,200/t (quotation expired, issued 2024-07-25)</t>
+          <t>Stranded: valued at the disposal netback. Upside bound is the Argus/Fastmarkets kosher crude 80% fob assessment, 24-31 c/lb</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>NO free US bulk assessment exists. Note the reflexivity: triacetin is made FROM glycerol, so its price partly tracks our own feedstock cost.</t>
+          <t>CRITICAL AND UNRESOLVED - this single price decides between a $3.5M project and a $22M one. SET BY STRANDING_BARRIER = 'unresolved'. Stripping methanol is assumed NOT to restore market access, so the de-methanolised material remains stranded and is valued at the disposal netback. The HIGH bound carries the case where methanol was the barrier after all. Flip STRANDING_BARRIER to 'methanol' to price that case.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>acetic_anhydride</t>
+          <t>propylene_glycol</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>900</v>
+        <v>2000</v>
       </c>
       <c r="C19" t="n">
-        <v>840</v>
+        <v>1600</v>
       </c>
       <c r="D19" t="n">
-        <v>970</v>
+        <v>2800</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4597,125 +4830,121 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>sourced</t>
+          <t>placeholder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ExpertMarketResearch US $890/t (Q2 2026), 2026 US range $870-940/t; IMARC North America $840/t (Jul 2026); businessanalytiq North America $970/t (Sep 2026); Intratec US export fob $870/t (Nov 2025)</t>
+          <t>IndexBox US Propylene Glycol USP market report, contract range $1.20-1.80/lb USP and $0.85-1.25/lb industrial grade (2026)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Good convergence across four independent sources.</t>
+          <t>LOW CONFIDENCE. IndexBox is a market-report aggregator, not a price reporting agency, and its own USP and world-spot figures are mutually inconsistent once units are reconciled. Range is wide on purpose. Immaterial to the conclusion: D1 fails by $50M+.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>caustic_soda</t>
+          <t>solketal</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>740</v>
+        <v>3000</v>
       </c>
       <c r="C20" t="n">
-        <v>460</v>
+        <v>2400</v>
       </c>
       <c r="D20" t="n">
-        <v>900</v>
+        <v>6200</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>$/t (100% NaOH dry basis)</t>
+          <t>$/t</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>sourced</t>
+          <t>placeholder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Argus Chlor-Alkali, fob USGC contract $655-690/dry short ton = $722-761/dry metric tonne NaOH (Apr 2026); fob USGC export spot $460-490/dmt (wk 21, ~2026-05-22)</t>
+          <t>~$3,000/t cited in Sustainable Chemistry 2021, 2(2), 17 (10.3390/suschem2020017); RMB 45,000/t (97%, China, Apr 2025) per Valuates/QYResearch = ~$6,200/t</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>BASIS WARNING: US caustic is quoted per DRY tonne of 100% NaOH. The contract range equates to $361-381 per tonne of as-delivered 50% liquor. Domestic contract is the right basis for a small inland buyer; export spot is the low bound.</t>
-        </is>
-      </c>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>crude_glycerol</t>
+          <t>triacetin</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="C21" t="n">
-        <v>176</v>
+        <v>1200</v>
       </c>
       <c r="D21" t="n">
-        <v>630</v>
+        <v>1400</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>$/t crude (80% basis)</t>
+          <t>$/t</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>sourced</t>
+          <t>placeholder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Argus Glycerine, US Midwest crude 80% fob, four dated assessments 2022-01-06 / ~2024-01 / 2025-10-01 / 2026-04-16 (17-19 c/lb latest)</t>
+          <t>ChemAnalyst CFR Mexico $1,400/t (Feb 2026); Chemball fob Shanghai ~$1,200/t (quotation expired, issued 2024-07-25)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Base is the approximate median of four dated observations (~18 c/lb). Low is the Jan-2024 trough (8 c/lb); high is the Jan-2022 peak (28.5 c/lb). Current spot (Apr 2026) is 17-19 c/lb = $375-419/t, i.e. near the LOW end even as refined sits near its high.</t>
+          <t>NO free US bulk assessment exists. Note the reflexivity: triacetin is made FROM glycerol, so its price partly tracks our own feedstock cost.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>acetic_anhydride</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.098</v>
+        <v>900</v>
       </c>
       <c r="C22" t="n">
-        <v>0.08599999999999999</v>
+        <v>840</v>
       </c>
       <c r="D22" t="n">
-        <v>0.128</v>
+        <v>970</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>$/kWh</t>
+          <t>$/t</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4725,38 +4954,38 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>EIA Electric Power Monthly Table 5.6.A, New York industrial 10.17 c/kWh (Jun 2026, vs 9.21 Jun 2025); NYSERDA monthly NY industrial 2026: Jan 12.8, Feb 10.9, Mar 8.7, Apr 8.6, May 9.6 - YTD average 10.1 c/kWh; CY2025 average 9.5 c/kWh</t>
+          <t>ExpertMarketResearch US $890/t (Q2 2026), 2026 US range $870-940/t; IMARC North America $840/t (Jul 2026); businessanalytiq North America $970/t (Sep 2026); Intratec US export fob $870/t (Nov 2025)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>All-in average (total bill divided by kWh, including demand charges and taxes), which is the correct basis for a TEA. The 8.6-12.8 c/kWh seasonal envelope is wide enough to matter if the load were seasonal; this process runs base-load so the annual average applies. EIA flags 2025-26 values as preliminary.</t>
+          <t>Good convergence across four independent sources.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>epichlorohydrin</t>
+          <t>caustic_soda</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1550</v>
+        <v>740</v>
       </c>
       <c r="C23" t="n">
-        <v>1350</v>
+        <v>460</v>
       </c>
       <c r="D23" t="n">
-        <v>2050</v>
+        <v>900</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>$/t</t>
+          <t>$/t (100% NaOH dry basis)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4766,38 +4995,38 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Intratec US fob export $1,630/t (Nov 2025); Procurement Resource USA CIF $1,705.82/t (Jun 2026); IMARC North America $1,350/t (Aug 2026); Argus assessed China exw $1,902/t (2026-04-16)</t>
+          <t>Argus Chlor-Alkali, fob USGC contract $655-690/dry short ton = $722-761/dry metric tonne NaOH (Apr 2026); fob USGC export spot $460-490/dmt (wk 21, ~2026-05-22)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SunSirs reports Chinese capacity additions of ~140 kt in 2024 and ~170 kt in 2025 against much slower demand growth, and a 46.9% intra-year price swing in 2025. Structurally oversupplied.</t>
+          <t>BASIS WARNING: US caustic is quoted per DRY tonne of 100% NaOH. The contract range equates to $361-381 per tonne of as-delivered 50% liquor. Domestic contract is the right basis for a small inland buyer; export spot is the low bound.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>natural_gas</t>
+          <t>crude_disposal_cost</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13</v>
+        <v>200</v>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>180</v>
       </c>
       <c r="D24" t="n">
-        <v>16.5</v>
+        <v>220</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>$/MMBtu</t>
+          <t>$/t crude (a COST, entered positive)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4807,38 +5036,38 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>EIA New York industrial natural gas price: $14.71/Mcf (Feb 2026), $16.27/Mcf (latest monthly in series); converted at 1.037 MMBtu/Mcf</t>
+          <t>Client invoice: $1.8-2.2M/yr paid against the 10,000 t/yr crude glycerol stream</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>New York industrial retail gas is roughly 2.5-3x the US average ($4.26-5.23/Mcf per EIA STEO Aug 2026). This penalises every evaporation- and distillation-heavy route and is a genuine siting disadvantage for this client.</t>
+          <t>THE BEST-SOURCED NUMBER IN THIS STUDY - a cost the client already incurs, not a market assessment. Cross-check: at ~1.23 kg/L, 10,000 t/yr is ~2.15M gal, so $1.8-2.2M/yr is $0.84-1.02/gal, at or above the top of the $0.25-1.00/gal band cited for trap grease under 'acid_oil_ffa' - for material that is NOT hazardous (confirmed with the client: no RCRA D001 ignitability classification). TWO OPEN ITEMS. (1) The disposal MECHANISM is unnamed - high-COD POTW surcharge, incineration, fuel blending, long-haul licensed hauling or an AD gate fee all reach this number but escalate differently. (2) Crude glycerol is a valued anaerobic-digestion co-substrate, so paying ~$1/gal to destroy it is anomalous; route B3 is NOT YET MODELLED and it sets the ceiling on this cost. This is also a CONTRACT, so its term and escalator govern when the avoided cost can actually be booked - see FIN.avoided_cost_timing_note.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sulfuric_acid</t>
+          <t>crude_glycerol</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>875</v>
+        <v>-200</v>
       </c>
       <c r="C25" t="n">
-        <v>300</v>
+        <v>-220</v>
       </c>
       <c r="D25" t="n">
-        <v>950</v>
+        <v>-180</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>$/t (93%, delivered)</t>
+          <t>$/t crude (NEGATIVE - this stream is a liability)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4848,38 +5077,38 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Westchester County NY contract award RFB-WC-26173, sulphuric acid 93% in bulk, DELIVERED upstate New York, $6.07/gal; converted at SG 1.835 (6.945 kg/gal) = $874/t</t>
+          <t>Client invoice: $1.8-2.2M/yr paid against the 10,000 t/yr crude glycerol stream</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ANCHORED ON A NEW YORK DELIVERED CONTRACT, NOT AN INDEX. Published benchmarks for this commodity span $40-457/t (IndexBox Gulf spot $40-70/t; IMARC North America $166/t; ExpertMarketResearch US $295-345/t; Procurement Resource USA CIF $457/t) because they describe 1,000-10,000 t Gulf Coast lots. Tank-truck freight to the Finger Lakes dominates the delivered price at our 91 t/yr consumption. The low bound retains an index-like value to show the item is immaterial either way.</t>
+          <t>NETBACK ON THE CLIENT'S OWN CRUDE, derived as -1 x crude_disposal_cost. Negative because the stream is stranded: the client pays to move it. Charged to every route as the feed transfer price, so route A1 (dispose) still scores EXACTLY zero margin by construction and remains the hurdle - only the meaning of that zero changes, from 'collect $4.0M/yr' to 'pay $2.0M/yr'. Do NOT override this without also overriding crude_disposal_cost, or the baseline stops netting to zero.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>technical_glycerine</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1250</v>
+        <v>0.098</v>
       </c>
       <c r="C26" t="n">
-        <v>772</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>2271</v>
+        <v>0.128</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>$/t (99.5%)</t>
+          <t>$/kWh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4889,56 +5118,261 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Argus Glycerine, technical grade 99.5% bulk delivered US Midwest; Apr 2026 assessment 68-70 c/lb = $1,499-1,543/t</t>
+          <t>EIA Electric Power Monthly Table 5.6.A, New York industrial 10.17 c/kWh (Jun 2026, vs 9.21 Jun 2025); NYSERDA monthly NY industrial 2026: Jan 12.8, Feb 10.9, Mar 8.7, Apr 8.6, May 9.6 - YTD average 10.1 c/kWh; CY2025 average 9.5 c/kWh</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Base $1,250/t is mid-cycle, deliberately BELOW the Apr-2026 spot of ~$1,521/t, which Argus attributes to import disruption via the Strait of Hormuz and reduced Indonesian/Malaysian arrivals.</t>
+          <t>All-in average (total bill divided by kWh, including demand charges and taxes), which is the correct basis for a TEA. The 8.6-12.8 c/kWh seasonal envelope is wide enough to matter if the load were seasonal; this process runs base-load so the annual average applies. EIA flags 2025-26 values as preliminary.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>epichlorohydrin</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1550</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2050</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>$/t</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Intratec US fob export $1,630/t (Nov 2025); Procurement Resource USA CIF $1,705.82/t (Jun 2026); IMARC North America $1,350/t (Aug 2026); Argus assessed China exw $1,902/t (2026-04-16)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>SunSirs reports Chinese capacity additions of ~140 kt in 2024 and ~170 kt in 2025 against much slower demand growth, and a 46.9% intra-year price swing in 2025. Structurally oversupplied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>merchant_crude_glycerol</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>400</v>
+      </c>
+      <c r="C28" t="n">
+        <v>176</v>
+      </c>
+      <c r="D28" t="n">
+        <v>630</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>$/t crude (80% basis)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Argus Glycerine, US Midwest crude 80% fob, four dated assessments 2022-01-06 / ~2024-01 / 2025-10-01 / 2026-04-16 (17-19 c/lb latest)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Base is the approximate median of four dated observations (~18 c/lb). Low is the Jan-2024 trough (8 c/lb); high is the Jan-2022 peak (28.5 c/lb). UNCHANGED from the positive-netback basis, and still the right price for THIRD-PARTY crude: under client-specific stranding the client's neighbours are not stranded, so E3 must BUY their crude at the assessment rather than be paid to take it. Conflating this with the client's own netback overstates E3 by ~$12M/yr of EBITDA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>natural_gas</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>13</v>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>$/MMBtu</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>EIA New York industrial natural gas price: $14.71/Mcf (Feb 2026), $16.27/Mcf (latest monthly in series); converted at 1.037 MMBtu/Mcf</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>New York industrial retail gas is roughly 2.5-3x the US average ($4.26-5.23/Mcf per EIA STEO Aug 2026). This penalises every evaporation- and distillation-heavy route and is a genuine siting disadvantage for this client.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sulfuric_acid</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>875</v>
+      </c>
+      <c r="C30" t="n">
+        <v>300</v>
+      </c>
+      <c r="D30" t="n">
+        <v>950</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>$/t (93%, delivered)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Westchester County NY contract award RFB-WC-26173, sulphuric acid 93% in bulk, DELIVERED upstate New York, $6.07/gal; converted at SG 1.835 (6.945 kg/gal) = $874/t</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ANCHORED ON A NEW YORK DELIVERED CONTRACT, NOT AN INDEX. Published benchmarks for this commodity span $40-457/t (IndexBox Gulf spot $40-70/t; IMARC North America $166/t; ExpertMarketResearch US $295-345/t; Procurement Resource USA CIF $457/t) because they describe 1,000-10,000 t Gulf Coast lots. Tank-truck freight to the Finger Lakes dominates the delivered price at our 91 t/yr consumption. The low bound retains an index-like value to show the item is immaterial either way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>technical_glycerine</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C31" t="n">
+        <v>772</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2271</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>$/t (99.5%)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>sourced</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Argus Glycerine, technical grade 99.5% bulk delivered US Midwest; Apr 2026 assessment 68-70 c/lb = $1,499-1,543/t</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Base $1,250/t is mid-cycle, deliberately BELOW the Apr-2026 spot of ~$1,521/t, which Argus attributes to import disruption via the Strait of Hormuz and reduced Indonesian/Malaysian arrivals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>usp_glycerine</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B32" t="n">
         <v>1530</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C32" t="n">
         <v>959</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D32" t="n">
         <v>2734</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>$/t (99.7% USP)</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>sourced</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Argus Glycerine, USP vegetable refined 99.7% bulk delivered US Midwest; Apr 2026 assessment 75-80 c/lb = $1,653-1,764/t</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>Base set at technical base + $280/t, the median USP-technical premium across the four dated observations. NOTE: if the client's feedstock is tallow/UCO rather than vegetable, the applicable assessment is USP tallow, which runs 3-6 c/lb BELOW USP vegetable.</t>
         </is>
@@ -5238,7 +5672,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sell crude glycerol as-is to a merchant refiner</t>
+          <t>Continue paying for disposal (do nothing)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5292,7 +5726,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pay for disposal / anaerobic digestion offtake</t>
+          <t>Disposal cost escalates (downside bound)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5342,7 +5776,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Value-destroying by inspection whenever the crude market is positive. Retained only as the downside bound.</t>
+          <t>Not a choice - a risk. Retained only as the downside bound on the baseline itself.</t>
         </is>
       </c>
     </row>
@@ -6690,47 +7124,45 @@
         <v>1.114052064428312</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="K2" t="n">
-        <v>5.641192607772425</v>
+        <v>-0.3588073922275745</v>
       </c>
       <c r="L2" t="n">
         <v>4.106798222140399</v>
       </c>
       <c r="M2" t="n">
-        <v>1.751191023883594</v>
+        <v>7.751191023883595</v>
       </c>
       <c r="N2" t="n">
-        <v>175.1191023883594</v>
+        <v>775.1191023883595</v>
       </c>
       <c r="O2" t="n">
         <v>25.96901970905098</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.01167264418736125</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.1693708345189042</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.204114743721052</v>
       </c>
       <c r="R2" t="n">
-        <v>-17.01480446510902</v>
+        <v>12.75053836650466</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01881335668910433</v>
+        <v>0.2040157472514001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Regional aggregation refinery (30,000 t/yr crude)</t>
+          <t>Purify to technical grade (99.5%)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6739,7 +7171,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -6747,57 +7179,57 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>21747.13567839196</v>
+        <v>7249.045226130654</v>
       </c>
       <c r="G3" t="n">
         <v>1170</v>
       </c>
       <c r="H3" t="n">
-        <v>25.44414874371859</v>
+        <v>8.481382914572865</v>
       </c>
       <c r="I3" t="n">
-        <v>3.342156193284936</v>
+        <v>1.114052064428312</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="K3" t="n">
-        <v>18.57354355871755</v>
+        <v>-0.3421521470941498</v>
       </c>
       <c r="L3" t="n">
-        <v>5.61555691806876</v>
+        <v>3.138633694926773</v>
       </c>
       <c r="M3" t="n">
-        <v>4.597204460217218</v>
+        <v>6.798953431168553</v>
       </c>
       <c r="N3" t="n">
-        <v>153.2401486739073</v>
+        <v>679.8953431168553</v>
       </c>
       <c r="O3" t="n">
-        <v>42.04165472649503</v>
+        <v>21.74738526912969</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03245088310320887</v>
+        <v>0.1880314534131299</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.49158994533793</v>
+        <v>3.556612576177478</v>
       </c>
       <c r="R3" t="n">
-        <v>-13.59445609218239</v>
+        <v>14.06432884394639</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05145652557333369</v>
+        <v>0.2344876467967214</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Purify to technical grade (99.5%)</t>
+          <t>Regional aggregation refinery (30,000 t/yr crude)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6806,7 +7238,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -6814,59 +7246,57 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7249.045226130654</v>
+        <v>21747.13567839196</v>
       </c>
       <c r="G4" t="n">
         <v>1170</v>
       </c>
       <c r="H4" t="n">
-        <v>8.481382914572865</v>
+        <v>25.44414874371859</v>
       </c>
       <c r="I4" t="n">
-        <v>1.114052064428312</v>
+        <v>3.342156193284936</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="K4" t="n">
-        <v>5.65784785290585</v>
+        <v>12.57354355871755</v>
       </c>
       <c r="L4" t="n">
-        <v>3.138633694926773</v>
+        <v>5.61555691806876</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7989534311685543</v>
+        <v>10.59720446021722</v>
       </c>
       <c r="N4" t="n">
-        <v>79.89534311685543</v>
+        <v>353.2401486739073</v>
       </c>
       <c r="O4" t="n">
-        <v>21.74738526912969</v>
+        <v>42.04165472649503</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.02752979132779295</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.1427094549516792</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.340946371977351</v>
       </c>
       <c r="R4" t="n">
-        <v>-15.44519156405563</v>
+        <v>15.50503231007985</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.05188871099054526</v>
+        <v>0.1881007470456229</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>De-methanolised feed-grade glycerin</t>
+          <t>Combust for process steam at the biodiesel plant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6879,66 +7309,66 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Feed-grade glycerin (~87.5% glycerol, low methanol)</t>
+          <t>Displaced natural gas</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>9145</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.801125</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.513</v>
+        <v>2.052556368311963</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="K5" t="n">
-        <v>4.103296433577007</v>
+        <v>-1.984</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7453846375634726</v>
+        <v>0.9270708000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4654439288595212</v>
+        <v>3.109485568311962</v>
       </c>
       <c r="N5" t="n">
-        <v>46.54439288595211</v>
+        <v>310.9485568311962</v>
       </c>
       <c r="O5" t="n">
-        <v>3.505294610902948</v>
+        <v>8.351577000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.05101085929025394</v>
+        <v>0.2322020677712547</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.453949508206637</v>
+        <v>3.036108417628954</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.7180082959550149</v>
+        <v>7.644371802708527</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07781002259152592</v>
+        <v>0.2763058589879799</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sell crude glycerol as-is to a merchant refiner</t>
+          <t>Propylene glycol via hydrogenolysis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -6946,60 +7376,68 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(none - feed sold directly)</t>
+          <t>Propylene glycol (industrial/USP)</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>4043.493654612513</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1920</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>7.763507816856025</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>1.003707236842105</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>1.446350844108536</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>6.256006002882129</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.064858206707464</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>106.4858206707464</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+        <v>31.12442808201108</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.02966086356646925</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
       <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
+        <v>-22.53350967005572</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.05637583366371091</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>De-icer / dust suppressant blend component</t>
+          <t>Continue paying for disposal (do nothing)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -7007,35 +7445,35 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>De-icer blend component</t>
+          <t>(none - stream disposed of)</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>9145</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.069525</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4032</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.333675</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-33.3675</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -7043,7 +7481,7 @@
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>-2.029120721894851</v>
+        <v>0</v>
       </c>
       <c r="S7" t="inlineStr"/>
     </row>
@@ -7081,28 +7519,28 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4.171</v>
+        <v>-1.316</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="K8" t="n">
-        <v>4.103296433577007</v>
+        <v>-1.896703566422994</v>
       </c>
       <c r="L8" t="n">
         <v>0.6653846375634727</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5976810711404789</v>
+        <v>-0.08468107114047883</v>
       </c>
       <c r="N8" t="n">
-        <v>-59.76810711404789</v>
+        <v>-8.468107114047884</v>
       </c>
       <c r="O8" t="n">
         <v>3.505294610902948</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2290446702730219</v>
+        <v>-0.08269463213233227</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -7110,24 +7548,26 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>-6.826479162808219</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
+        <v>-3.706859981472909</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.2290056265596219</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Membrane / ion-exchange-led purification (no distillation)</t>
+          <t>De-methanolised feed-grade glycerin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -7135,60 +7575,68 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Purified glycerine 93.9%</t>
+          <t>Feed-grade glycerin (~87.5% glycerol, low methanol)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7343.98296059638</v>
+        <v>9145</v>
       </c>
       <c r="G9" t="n">
-        <v>445</v>
+        <v>-200</v>
       </c>
       <c r="H9" t="n">
-        <v>3.268072417465389</v>
+        <v>-1.829</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.513</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>-1.896703566422994</v>
       </c>
       <c r="L9" t="n">
-        <v>1.512</v>
+        <v>0.7453846375634726</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.243927582534611</v>
+        <v>-0.1646810711404788</v>
       </c>
       <c r="N9" t="n">
-        <v>-224.3927582534611</v>
+        <v>-16.46810711404788</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+        <v>3.505294610902948</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.1055172501659681</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
       <c r="R9" t="n">
-        <v>-13.64561311501431</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
+        <v>-4.19335030214898</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.3867773236909647</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Combust for process steam at the biodiesel plant</t>
+          <t>De-icer / dust suppressant blend component</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -7196,61 +7644,55 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Displaced natural gas</t>
+          <t>De-icer blend component</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>9145</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-280</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-2.5606</v>
       </c>
       <c r="I10" t="n">
-        <v>2.052556368311963</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="K10" t="n">
-        <v>4.016</v>
+        <v>-2</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9270708000000001</v>
+        <v>0.4032</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.890514431688038</v>
+        <v>-0.9638</v>
       </c>
       <c r="N10" t="n">
-        <v>-289.0514431688038</v>
+        <v>-96.38</v>
       </c>
       <c r="O10" t="n">
-        <v>8.351577000000001</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.4046406123882997</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>-25.18249474412187</v>
+        <v>-5.860992138344971</v>
       </c>
       <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pay for disposal / anaerobic digestion offtake</t>
+          <t>Membrane / ion-exchange-led purification (no distillation)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7263,35 +7705,35 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(none - disposal)</t>
+          <t>Purified glycerine 93.9%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>7343.98296059638</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-280</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-2.056315228966986</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="K11" t="n">
-        <v>4.8</v>
+        <v>-2</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.512</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.8</v>
+        <v>-1.568315228966986</v>
       </c>
       <c r="N11" t="n">
-        <v>-480</v>
+        <v>-156.8315228966986</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -7299,19 +7741,19 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>-29.18941924056429</v>
+        <v>-9.537127233266444</v>
       </c>
       <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Propylene glycol via hydrogenolysis</t>
+          <t>Disposal cost escalates (downside bound)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7324,49 +7766,43 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Propylene glycol (industrial/USP)</t>
+          <t>(none - disposal)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4043.493654612513</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1920</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>7.763507816856025</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1.003707236842105</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="K12" t="n">
-        <v>7.446350844108537</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>6.256006002882129</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.935141793292536</v>
+        <v>-2</v>
       </c>
       <c r="N12" t="n">
-        <v>-493.5141793292536</v>
+        <v>-200</v>
       </c>
       <c r="O12" t="n">
-        <v>31.12442808201108</v>
-      </c>
-      <c r="P12" t="n">
-        <v>-0.2170982713922996</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>-58.35297999721605</v>
+        <v>-12.16225801690179</v>
       </c>
       <c r="S12" t="inlineStr"/>
     </row>
@@ -7928,14 +8364,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sell crude glycerol as-is to a merchant refiner</t>
+          <t>Continue paying for disposal (do nothing)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4000000</v>
+        <v>-2000000</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -7950,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -7980,10 +8416,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -8001,7 +8437,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4000000</v>
+        <v>-2000000</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -8019,7 +8455,7 @@
         <v>10500</v>
       </c>
       <c r="I3" t="n">
-        <v>4103296.433577006</v>
+        <v>-1896703.566422994</v>
       </c>
       <c r="J3" t="n">
         <v>1.92</v>
@@ -8046,16 +8482,16 @@
         <v>745384.6375634726</v>
       </c>
       <c r="R3" t="n">
-        <v>4801125</v>
+        <v>-1829000</v>
       </c>
       <c r="S3" t="n">
         <v>513000</v>
       </c>
       <c r="T3" t="n">
-        <v>5314125</v>
+        <v>-1316000</v>
       </c>
       <c r="U3" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
     </row>
     <row r="4">
@@ -8070,7 +8506,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4000000</v>
+        <v>-2000000</v>
       </c>
       <c r="D4" t="n">
         <v>202768.4790730412</v>
@@ -8088,7 +8524,7 @@
         <v>79456.33136562814</v>
       </c>
       <c r="I4" t="n">
-        <v>5657847.85290585</v>
+        <v>-342152.1470941498</v>
       </c>
       <c r="J4" t="n">
         <v>7.199999999999999</v>
@@ -8124,7 +8560,7 @@
         <v>9595434.979001177</v>
       </c>
       <c r="U4" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
     </row>
     <row r="5">
@@ -8139,7 +8575,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4000000</v>
+        <v>-2000000</v>
       </c>
       <c r="D5" t="n">
         <v>202031.5893759019</v>
@@ -8157,7 +8593,7 @@
         <v>79007.38135577933</v>
       </c>
       <c r="I5" t="n">
-        <v>5641192.607772426</v>
+        <v>-358807.3922275745</v>
       </c>
       <c r="J5" t="n">
         <v>8.640000000000001</v>
@@ -8193,7 +8629,7 @@
         <v>11499181.85379642</v>
       </c>
       <c r="U5" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
     </row>
     <row r="6">
@@ -8208,7 +8644,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4000000</v>
+        <v>-2000000</v>
       </c>
       <c r="D6" t="n">
         <v>10208305.43721912</v>
@@ -8226,7 +8662,7 @@
         <v>238368.9940968844</v>
       </c>
       <c r="I6" t="n">
-        <v>18573543.55871755</v>
+        <v>12573543.55871755</v>
       </c>
       <c r="J6" t="n">
         <v>10.57608507312053</v>
@@ -8262,7 +8698,7 @@
         <v>28786304.93700353</v>
       </c>
       <c r="U6" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
     </row>
   </sheetData>
@@ -8971,12 +9407,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Purchased / disposal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Crude glycerol sold fob plant</t>
+          <t>Crude glycerol disposal, as invoiced today</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -8984,18 +9420,18 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>crude_glycerol</t>
+          <t>crude_disposal_cost</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>4000000</v>
+        <v>2000000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10,000 t/yr as-is, no processing</t>
+          <t>10,000 t/yr at the invoiced $200/t; $2.0M/yr</t>
         </is>
       </c>
     </row>
@@ -9164,7 +9600,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>crude_glycerol</t>
+          <t>second_cut_glycerine</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -9175,7 +9611,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3% of glycerol per the Lurgi yield block</t>
+          <t>3% of glycerol per the Lurgi yield block. Priced on its own key, NOT the client's stranded netback: it is salt-free and methanol-free, so it is assumed saleable even while the raw 80% crude is not.</t>
         </is>
       </c>
     </row>
@@ -9452,7 +9888,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>crude_glycerol</t>
+          <t>second_cut_glycerine</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -9463,7 +9899,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3% of glycerol per the Lurgi yield block</t>
+          <t>3% of glycerol per the Lurgi yield block. Priced on its own key, NOT the client's stranded netback: it is salt-free and methanol-free, so it is assumed saleable even while the raw 80% crude is not.</t>
         </is>
       </c>
     </row>
@@ -9740,7 +10176,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>crude_glycerol</t>
+          <t>second_cut_glycerine</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -9751,7 +10187,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3% of glycerol per the Lurgi yield block</t>
+          <t>3% of glycerol per the Lurgi yield block. Priced on its own key, NOT the client's stranded netback: it is salt-free and methanol-free, so it is assumed saleable even while the raw 80% crude is not.</t>
         </is>
       </c>
     </row>
@@ -9776,7 +10212,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>crude_glycerol</t>
+          <t>merchant_crude_glycerol</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -9787,7 +10223,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>20,000 t/yr bought in at the SAME Argus assessment used for the internal transfer price - no discount assumed</t>
+          <t>20,000 t/yr BOUGHT at the Argus merchant assessment, no discount assumed. Deliberately NOT priced at the client's own negative netback: the stranding is client-specific, so the neighbours still have a market and will not pay a gate fee. Pricing this line at the client's netback would credit E3 a phantom ~$12M/yr.</t>
         </is>
       </c>
     </row>
@@ -10858,22 +11294,22 @@
         <v>-0</v>
       </c>
       <c r="F21" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="G21" t="n">
         <v>615563.9316707617</v>
       </c>
       <c r="H21" t="n">
-        <v>-150120.0028112405</v>
+        <v>-780245.0028112405</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-150120.0028112405</v>
+        <v>-780245.0028112405</v>
       </c>
       <c r="K21" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
@@ -10900,22 +11336,22 @@
         <v>-0</v>
       </c>
       <c r="F22" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="G22" t="n">
         <v>984902.2906732187</v>
       </c>
       <c r="H22" t="n">
-        <v>-519458.3618136975</v>
+        <v>-1149583.361813697</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-519458.3618136975</v>
+        <v>-1149583.361813697</v>
       </c>
       <c r="K22" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="L22" t="n">
         <v>1</v>
@@ -10942,22 +11378,22 @@
         <v>-0</v>
       </c>
       <c r="F23" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="G23" t="n">
         <v>590941.3744039312</v>
       </c>
       <c r="H23" t="n">
-        <v>-125497.44554441</v>
+        <v>-755622.44554441</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-125497.44554441</v>
+        <v>-755622.44554441</v>
       </c>
       <c r="K23" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -10984,22 +11420,22 @@
         <v>-0</v>
       </c>
       <c r="F24" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="G24" t="n">
         <v>354564.8246423587</v>
       </c>
       <c r="H24" t="n">
-        <v>110879.1042171625</v>
+        <v>-519245.8957828375</v>
       </c>
       <c r="I24" t="n">
-        <v>28828.56709646224</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>82050.53712070023</v>
+        <v>-519245.8957828375</v>
       </c>
       <c r="K24" t="n">
-        <v>436615.3617630589</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="L24" t="n">
         <v>1</v>
@@ -11026,22 +11462,22 @@
         <v>-0</v>
       </c>
       <c r="F25" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="G25" t="n">
         <v>354564.8246423587</v>
       </c>
       <c r="H25" t="n">
-        <v>110879.1042171625</v>
+        <v>-519245.8957828375</v>
       </c>
       <c r="I25" t="n">
-        <v>28828.56709646224</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>82050.53712070023</v>
+        <v>-519245.8957828375</v>
       </c>
       <c r="K25" t="n">
-        <v>436615.3617630589</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="L25" t="n">
         <v>1</v>
@@ -11068,22 +11504,22 @@
         <v>-0</v>
       </c>
       <c r="F26" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="G26" t="n">
         <v>177282.4123211793</v>
       </c>
       <c r="H26" t="n">
-        <v>288161.5165383418</v>
+        <v>-341963.4834616582</v>
       </c>
       <c r="I26" t="n">
-        <v>74921.99429996888</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>213239.5222383729</v>
+        <v>-341963.4834616582</v>
       </c>
       <c r="K26" t="n">
-        <v>390521.9345595523</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -11110,22 +11546,22 @@
         <v>-0</v>
       </c>
       <c r="F27" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="I27" t="n">
-        <v>121015.4215034755</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>344428.5073560457</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="K27" t="n">
-        <v>344428.5073560457</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="L27" t="n">
         <v>1</v>
@@ -11152,22 +11588,22 @@
         <v>-0</v>
       </c>
       <c r="F28" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="I28" t="n">
-        <v>121015.4215034755</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>344428.5073560457</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="K28" t="n">
-        <v>344428.5073560457</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="L28" t="n">
         <v>1</v>
@@ -11194,22 +11630,22 @@
         <v>-0</v>
       </c>
       <c r="F29" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="I29" t="n">
-        <v>121015.4215034755</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>344428.5073560457</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="K29" t="n">
-        <v>344428.5073560457</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -11236,22 +11672,22 @@
         <v>-0</v>
       </c>
       <c r="F30" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="I30" t="n">
-        <v>121015.4215034755</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>344428.5073560457</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="K30" t="n">
-        <v>344428.5073560457</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="L30" t="n">
         <v>1</v>
@@ -11278,22 +11714,22 @@
         <v>-0</v>
       </c>
       <c r="F31" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="I31" t="n">
-        <v>121015.4215034755</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>344428.5073560457</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="K31" t="n">
-        <v>344428.5073560457</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="L31" t="n">
         <v>1</v>
@@ -11320,22 +11756,22 @@
         <v>-0</v>
       </c>
       <c r="F32" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="I32" t="n">
-        <v>121015.4215034755</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>344428.5073560457</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="K32" t="n">
-        <v>344428.5073560457</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
@@ -11362,22 +11798,22 @@
         <v>-0</v>
       </c>
       <c r="F33" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="I33" t="n">
-        <v>121015.4215034755</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>344428.5073560457</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="K33" t="n">
-        <v>344428.5073560457</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="L33" t="n">
         <v>1</v>
@@ -11404,22 +11840,22 @@
         <v>-0</v>
       </c>
       <c r="F34" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="I34" t="n">
-        <v>121015.4215034755</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>344428.5073560457</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="K34" t="n">
-        <v>344428.5073560457</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="L34" t="n">
         <v>1</v>
@@ -11446,22 +11882,22 @@
         <v>-427474.95254914</v>
       </c>
       <c r="F35" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>465443.9288595212</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="I35" t="n">
-        <v>121015.4215034755</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>344428.5073560457</v>
+        <v>-164681.0711404788</v>
       </c>
       <c r="K35" t="n">
-        <v>771903.4599051857</v>
+        <v>262793.8814086612</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -11568,22 +12004,22 @@
         <v>-0</v>
       </c>
       <c r="F38" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="G38" t="n">
         <v>3819053.022871555</v>
       </c>
       <c r="H38" t="n">
-        <v>-3020099.591703</v>
+        <v>2979900.408296999</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>774774.1061572196</v>
       </c>
       <c r="J38" t="n">
-        <v>-3020099.591703</v>
+        <v>2205126.302139779</v>
       </c>
       <c r="K38" t="n">
-        <v>798953.4311685544</v>
+        <v>6024179.325011333</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
@@ -11610,22 +12046,22 @@
         <v>-0</v>
       </c>
       <c r="F39" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="G39" t="n">
         <v>6110484.836594488</v>
       </c>
       <c r="H39" t="n">
-        <v>-5311531.405425933</v>
+        <v>688468.5945740659</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>179001.8345892571</v>
       </c>
       <c r="J39" t="n">
-        <v>-5311531.405425933</v>
+        <v>509466.7599848087</v>
       </c>
       <c r="K39" t="n">
-        <v>798953.4311685544</v>
+        <v>6619951.596579297</v>
       </c>
       <c r="L39" t="n">
         <v>1</v>
@@ -11652,22 +12088,22 @@
         <v>-0</v>
       </c>
       <c r="F40" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="G40" t="n">
         <v>3666290.901956692</v>
       </c>
       <c r="H40" t="n">
-        <v>-2867337.470788138</v>
+        <v>3132662.529211861</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>814492.2575950839</v>
       </c>
       <c r="J40" t="n">
-        <v>-2867337.470788138</v>
+        <v>2318170.271616777</v>
       </c>
       <c r="K40" t="n">
-        <v>798953.4311685544</v>
+        <v>5984461.17357347</v>
       </c>
       <c r="L40" t="n">
         <v>1</v>
@@ -11694,22 +12130,22 @@
         <v>-0</v>
       </c>
       <c r="F41" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="G41" t="n">
         <v>2199774.541174015</v>
       </c>
       <c r="H41" t="n">
-        <v>-1400821.110005461</v>
+        <v>4599178.889994537</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1195786.51139858</v>
       </c>
       <c r="J41" t="n">
-        <v>-1400821.110005461</v>
+        <v>3403392.378595958</v>
       </c>
       <c r="K41" t="n">
-        <v>798953.4311685544</v>
+        <v>5603166.919769973</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
@@ -11736,22 +12172,22 @@
         <v>-0</v>
       </c>
       <c r="F42" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="G42" t="n">
         <v>2199774.541174015</v>
       </c>
       <c r="H42" t="n">
-        <v>-1400821.110005461</v>
+        <v>4599178.889994537</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1195786.51139858</v>
       </c>
       <c r="J42" t="n">
-        <v>-1400821.110005461</v>
+        <v>3403392.378595958</v>
       </c>
       <c r="K42" t="n">
-        <v>798953.4311685544</v>
+        <v>5603166.919769973</v>
       </c>
       <c r="L42" t="n">
         <v>1</v>
@@ -11778,22 +12214,22 @@
         <v>-0</v>
       </c>
       <c r="F43" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="G43" t="n">
         <v>1099887.270587008</v>
       </c>
       <c r="H43" t="n">
-        <v>-300933.8394184534</v>
+        <v>5699066.160581546</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1481757.201751202</v>
       </c>
       <c r="J43" t="n">
-        <v>-300933.8394184534</v>
+        <v>4217308.958830344</v>
       </c>
       <c r="K43" t="n">
-        <v>798953.4311685544</v>
+        <v>5317196.229417351</v>
       </c>
       <c r="L43" t="n">
         <v>1</v>
@@ -11820,22 +12256,22 @@
         <v>-0</v>
       </c>
       <c r="F44" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="I44" t="n">
-        <v>207727.8921038241</v>
+        <v>1767727.892103824</v>
       </c>
       <c r="J44" t="n">
-        <v>591225.5390647303</v>
+        <v>5031225.53906473</v>
       </c>
       <c r="K44" t="n">
-        <v>591225.5390647303</v>
+        <v>5031225.53906473</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
@@ -11862,22 +12298,22 @@
         <v>-0</v>
       </c>
       <c r="F45" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="I45" t="n">
-        <v>207727.8921038241</v>
+        <v>1767727.892103824</v>
       </c>
       <c r="J45" t="n">
-        <v>591225.5390647303</v>
+        <v>5031225.53906473</v>
       </c>
       <c r="K45" t="n">
-        <v>591225.5390647303</v>
+        <v>5031225.53906473</v>
       </c>
       <c r="L45" t="n">
         <v>1</v>
@@ -11904,22 +12340,22 @@
         <v>-0</v>
       </c>
       <c r="F46" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="I46" t="n">
-        <v>207727.8921038241</v>
+        <v>1767727.892103824</v>
       </c>
       <c r="J46" t="n">
-        <v>591225.5390647303</v>
+        <v>5031225.53906473</v>
       </c>
       <c r="K46" t="n">
-        <v>591225.5390647303</v>
+        <v>5031225.53906473</v>
       </c>
       <c r="L46" t="n">
         <v>1</v>
@@ -11946,22 +12382,22 @@
         <v>-0</v>
       </c>
       <c r="F47" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="I47" t="n">
-        <v>207727.8921038241</v>
+        <v>1767727.892103824</v>
       </c>
       <c r="J47" t="n">
-        <v>591225.5390647303</v>
+        <v>5031225.53906473</v>
       </c>
       <c r="K47" t="n">
-        <v>591225.5390647303</v>
+        <v>5031225.53906473</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
@@ -11988,22 +12424,22 @@
         <v>-0</v>
       </c>
       <c r="F48" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="I48" t="n">
-        <v>207727.8921038241</v>
+        <v>1767727.892103824</v>
       </c>
       <c r="J48" t="n">
-        <v>591225.5390647303</v>
+        <v>5031225.53906473</v>
       </c>
       <c r="K48" t="n">
-        <v>591225.5390647303</v>
+        <v>5031225.53906473</v>
       </c>
       <c r="L48" t="n">
         <v>1</v>
@@ -12030,22 +12466,22 @@
         <v>-0</v>
       </c>
       <c r="F49" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="I49" t="n">
-        <v>207727.8921038241</v>
+        <v>1767727.892103824</v>
       </c>
       <c r="J49" t="n">
-        <v>591225.5390647303</v>
+        <v>5031225.53906473</v>
       </c>
       <c r="K49" t="n">
-        <v>591225.5390647303</v>
+        <v>5031225.53906473</v>
       </c>
       <c r="L49" t="n">
         <v>1</v>
@@ -12072,22 +12508,22 @@
         <v>-0</v>
       </c>
       <c r="F50" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="I50" t="n">
-        <v>207727.8921038241</v>
+        <v>1767727.892103824</v>
       </c>
       <c r="J50" t="n">
-        <v>591225.5390647303</v>
+        <v>5031225.53906473</v>
       </c>
       <c r="K50" t="n">
-        <v>591225.5390647303</v>
+        <v>5031225.53906473</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
@@ -12114,22 +12550,22 @@
         <v>-0</v>
       </c>
       <c r="F51" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="I51" t="n">
-        <v>207727.8921038241</v>
+        <v>1767727.892103824</v>
       </c>
       <c r="J51" t="n">
-        <v>591225.5390647303</v>
+        <v>5031225.53906473</v>
       </c>
       <c r="K51" t="n">
-        <v>591225.5390647303</v>
+        <v>5031225.53906473</v>
       </c>
       <c r="L51" t="n">
         <v>1</v>
@@ -12156,22 +12592,22 @@
         <v>-2652120.154771913</v>
       </c>
       <c r="F52" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>798953.4311685544</v>
+        <v>6798953.431168553</v>
       </c>
       <c r="I52" t="n">
-        <v>207727.8921038241</v>
+        <v>1767727.892103824</v>
       </c>
       <c r="J52" t="n">
-        <v>591225.5390647303</v>
+        <v>5031225.53906473</v>
       </c>
       <c r="K52" t="n">
-        <v>3243345.693836643</v>
+        <v>7683345.693836642</v>
       </c>
       <c r="L52" t="n">
         <v>1</v>
@@ -12278,22 +12714,22 @@
         <v>-0</v>
       </c>
       <c r="F55" t="n">
-        <v>-149355.6042360594</v>
+        <v>5850644.395763941</v>
       </c>
       <c r="G55" t="n">
         <v>4560413.217199198</v>
       </c>
       <c r="H55" t="n">
-        <v>-4709768.821435258</v>
+        <v>1290231.178564743</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>335460.1064268333</v>
       </c>
       <c r="J55" t="n">
-        <v>-4709768.821435258</v>
+        <v>954771.0721379099</v>
       </c>
       <c r="K55" t="n">
-        <v>-149355.6042360598</v>
+        <v>5515184.289337108</v>
       </c>
       <c r="L55" t="n">
         <v>0.8169934640522876</v>
@@ -12320,22 +12756,22 @@
         <v>-0</v>
       </c>
       <c r="F56" t="n">
-        <v>-149355.6042360594</v>
+        <v>5850644.395763941</v>
       </c>
       <c r="G56" t="n">
         <v>7296661.147518716</v>
       </c>
       <c r="H56" t="n">
-        <v>-7446016.751754776</v>
+        <v>-1446016.751754775</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>-7446016.751754776</v>
+        <v>-1446016.751754775</v>
       </c>
       <c r="K56" t="n">
-        <v>-149355.6042360598</v>
+        <v>5850644.395763941</v>
       </c>
       <c r="L56" t="n">
         <v>0.8169934640522876</v>
@@ -12362,22 +12798,22 @@
         <v>-0</v>
       </c>
       <c r="F57" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="G57" t="n">
         <v>4377996.68851123</v>
       </c>
       <c r="H57" t="n">
-        <v>-2626805.664627636</v>
+        <v>3373194.335372365</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>877030.527196815</v>
       </c>
       <c r="J57" t="n">
-        <v>-2626805.664627636</v>
+        <v>2496163.80817555</v>
       </c>
       <c r="K57" t="n">
-        <v>1751191.023883594</v>
+        <v>6874160.49668678</v>
       </c>
       <c r="L57" t="n">
         <v>1</v>
@@ -12404,22 +12840,22 @@
         <v>-0</v>
       </c>
       <c r="F58" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="G58" t="n">
         <v>2626798.013106738</v>
       </c>
       <c r="H58" t="n">
-        <v>-875606.9892231436</v>
+        <v>5124393.010776857</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>1332342.182801983</v>
       </c>
       <c r="J58" t="n">
-        <v>-875606.9892231436</v>
+        <v>3792050.827974874</v>
       </c>
       <c r="K58" t="n">
-        <v>1751191.023883594</v>
+        <v>6418848.841081612</v>
       </c>
       <c r="L58" t="n">
         <v>1</v>
@@ -12446,22 +12882,22 @@
         <v>-0</v>
       </c>
       <c r="F59" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="G59" t="n">
         <v>2626798.013106738</v>
       </c>
       <c r="H59" t="n">
-        <v>-875606.9892231436</v>
+        <v>5124393.010776857</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1332342.182801983</v>
       </c>
       <c r="J59" t="n">
-        <v>-875606.9892231436</v>
+        <v>3792050.827974874</v>
       </c>
       <c r="K59" t="n">
-        <v>1751191.023883594</v>
+        <v>6418848.841081612</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
@@ -12488,22 +12924,22 @@
         <v>-0</v>
       </c>
       <c r="F60" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="G60" t="n">
         <v>1313399.006553369</v>
       </c>
       <c r="H60" t="n">
-        <v>437792.0173302253</v>
+        <v>6437792.017330226</v>
       </c>
       <c r="I60" t="n">
-        <v>113825.9245058586</v>
+        <v>1673825.924505859</v>
       </c>
       <c r="J60" t="n">
-        <v>323966.0928243668</v>
+        <v>4763966.092824368</v>
       </c>
       <c r="K60" t="n">
-        <v>1637365.099377736</v>
+        <v>6077365.099377736</v>
       </c>
       <c r="L60" t="n">
         <v>1</v>
@@ -12530,22 +12966,22 @@
         <v>-0</v>
       </c>
       <c r="F61" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="I61" t="n">
-        <v>455309.6662097345</v>
+        <v>2015309.666209735</v>
       </c>
       <c r="J61" t="n">
-        <v>1295881.35767386</v>
+        <v>5735881.35767386</v>
       </c>
       <c r="K61" t="n">
-        <v>1295881.35767386</v>
+        <v>5735881.35767386</v>
       </c>
       <c r="L61" t="n">
         <v>1</v>
@@ -12572,22 +13008,22 @@
         <v>-0</v>
       </c>
       <c r="F62" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="I62" t="n">
-        <v>455309.6662097345</v>
+        <v>2015309.666209735</v>
       </c>
       <c r="J62" t="n">
-        <v>1295881.35767386</v>
+        <v>5735881.35767386</v>
       </c>
       <c r="K62" t="n">
-        <v>1295881.35767386</v>
+        <v>5735881.35767386</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
@@ -12614,22 +13050,22 @@
         <v>-0</v>
       </c>
       <c r="F63" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="I63" t="n">
-        <v>455309.6662097345</v>
+        <v>2015309.666209735</v>
       </c>
       <c r="J63" t="n">
-        <v>1295881.35767386</v>
+        <v>5735881.35767386</v>
       </c>
       <c r="K63" t="n">
-        <v>1295881.35767386</v>
+        <v>5735881.35767386</v>
       </c>
       <c r="L63" t="n">
         <v>1</v>
@@ -12656,22 +13092,22 @@
         <v>-0</v>
       </c>
       <c r="F64" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="I64" t="n">
-        <v>455309.6662097345</v>
+        <v>2015309.666209735</v>
       </c>
       <c r="J64" t="n">
-        <v>1295881.35767386</v>
+        <v>5735881.35767386</v>
       </c>
       <c r="K64" t="n">
-        <v>1295881.35767386</v>
+        <v>5735881.35767386</v>
       </c>
       <c r="L64" t="n">
         <v>1</v>
@@ -12698,22 +13134,22 @@
         <v>-0</v>
       </c>
       <c r="F65" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="I65" t="n">
-        <v>455309.6662097345</v>
+        <v>2015309.666209735</v>
       </c>
       <c r="J65" t="n">
-        <v>1295881.35767386</v>
+        <v>5735881.35767386</v>
       </c>
       <c r="K65" t="n">
-        <v>1295881.35767386</v>
+        <v>5735881.35767386</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
@@ -12740,22 +13176,22 @@
         <v>-0</v>
       </c>
       <c r="F66" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="I66" t="n">
-        <v>455309.6662097345</v>
+        <v>2015309.666209735</v>
       </c>
       <c r="J66" t="n">
-        <v>1295881.35767386</v>
+        <v>5735881.35767386</v>
       </c>
       <c r="K66" t="n">
-        <v>1295881.35767386</v>
+        <v>5735881.35767386</v>
       </c>
       <c r="L66" t="n">
         <v>1</v>
@@ -12782,22 +13218,22 @@
         <v>-0</v>
       </c>
       <c r="F67" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="I67" t="n">
-        <v>455309.6662097345</v>
+        <v>2015309.666209735</v>
       </c>
       <c r="J67" t="n">
-        <v>1295881.35767386</v>
+        <v>5735881.35767386</v>
       </c>
       <c r="K67" t="n">
-        <v>1295881.35767386</v>
+        <v>5735881.35767386</v>
       </c>
       <c r="L67" t="n">
         <v>1</v>
@@ -12824,22 +13260,22 @@
         <v>-0</v>
       </c>
       <c r="F68" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="I68" t="n">
-        <v>455309.6662097345</v>
+        <v>2015309.666209735</v>
       </c>
       <c r="J68" t="n">
-        <v>1295881.35767386</v>
+        <v>5735881.35767386</v>
       </c>
       <c r="K68" t="n">
-        <v>1295881.35767386</v>
+        <v>5735881.35767386</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
@@ -12866,22 +13302,22 @@
         <v>-3166953.623054998</v>
       </c>
       <c r="F69" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>1751191.023883594</v>
+        <v>7751191.023883595</v>
       </c>
       <c r="I69" t="n">
-        <v>455309.6662097345</v>
+        <v>2015309.666209735</v>
       </c>
       <c r="J69" t="n">
-        <v>1295881.35767386</v>
+        <v>5735881.35767386</v>
       </c>
       <c r="K69" t="n">
-        <v>4462834.980728857</v>
+        <v>8902834.980728857</v>
       </c>
       <c r="L69" t="n">
         <v>1</v>
@@ -12988,22 +13424,22 @@
         <v>-0</v>
       </c>
       <c r="F72" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="G72" t="n">
         <v>7382924.732457664</v>
       </c>
       <c r="H72" t="n">
-        <v>-2785720.272240446</v>
+        <v>3214279.727759555</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>835712.7292174844</v>
       </c>
       <c r="J72" t="n">
-        <v>-2785720.272240446</v>
+        <v>2378566.99854207</v>
       </c>
       <c r="K72" t="n">
-        <v>4597204.460217218</v>
+        <v>9761491.730999734</v>
       </c>
       <c r="L72" t="n">
         <v>1</v>
@@ -13030,22 +13466,22 @@
         <v>-0</v>
       </c>
       <c r="F73" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="G73" t="n">
         <v>11812679.57193226</v>
       </c>
       <c r="H73" t="n">
-        <v>-7215475.111715044</v>
+        <v>-1215475.111715043</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>-7215475.111715044</v>
+        <v>-1215475.111715043</v>
       </c>
       <c r="K73" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="L73" t="n">
         <v>1</v>
@@ -13072,22 +13508,22 @@
         <v>-0</v>
       </c>
       <c r="F74" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="G74" t="n">
         <v>7087607.743159357</v>
       </c>
       <c r="H74" t="n">
-        <v>-2490403.282942139</v>
+        <v>3509596.717057862</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>912495.1464350442</v>
       </c>
       <c r="J74" t="n">
-        <v>-2490403.282942139</v>
+        <v>2597101.570622818</v>
       </c>
       <c r="K74" t="n">
-        <v>4597204.460217218</v>
+        <v>9684709.313782174</v>
       </c>
       <c r="L74" t="n">
         <v>1</v>
@@ -13114,22 +13550,22 @@
         <v>-0</v>
       </c>
       <c r="F75" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="G75" t="n">
         <v>4252564.645895614</v>
       </c>
       <c r="H75" t="n">
-        <v>344639.8143216036</v>
+        <v>6344639.814321605</v>
       </c>
       <c r="I75" t="n">
-        <v>89606.35172361694</v>
+        <v>1649606.351723617</v>
       </c>
       <c r="J75" t="n">
-        <v>255033.4625979867</v>
+        <v>4695033.462597988</v>
       </c>
       <c r="K75" t="n">
-        <v>4507598.108493601</v>
+        <v>8947598.108493602</v>
       </c>
       <c r="L75" t="n">
         <v>1</v>
@@ -13156,22 +13592,22 @@
         <v>-0</v>
       </c>
       <c r="F76" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="G76" t="n">
         <v>4252564.645895614</v>
       </c>
       <c r="H76" t="n">
-        <v>344639.8143216036</v>
+        <v>6344639.814321605</v>
       </c>
       <c r="I76" t="n">
-        <v>89606.35172361694</v>
+        <v>1649606.351723617</v>
       </c>
       <c r="J76" t="n">
-        <v>255033.4625979867</v>
+        <v>4695033.462597988</v>
       </c>
       <c r="K76" t="n">
-        <v>4507598.108493601</v>
+        <v>8947598.108493602</v>
       </c>
       <c r="L76" t="n">
         <v>1</v>
@@ -13198,22 +13634,22 @@
         <v>-0</v>
       </c>
       <c r="F77" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="G77" t="n">
         <v>2126282.322947807</v>
       </c>
       <c r="H77" t="n">
-        <v>2470922.137269411</v>
+        <v>8470922.137269411</v>
       </c>
       <c r="I77" t="n">
-        <v>642439.7556900468</v>
+        <v>2202439.755690047</v>
       </c>
       <c r="J77" t="n">
-        <v>1828482.381579364</v>
+        <v>6268482.381579364</v>
       </c>
       <c r="K77" t="n">
-        <v>3954764.704527171</v>
+        <v>8394764.704527171</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
@@ -13240,22 +13676,22 @@
         <v>-0</v>
       </c>
       <c r="F78" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="I78" t="n">
-        <v>1195273.159656477</v>
+        <v>2755273.159656477</v>
       </c>
       <c r="J78" t="n">
-        <v>3401931.300560741</v>
+        <v>7841931.300560742</v>
       </c>
       <c r="K78" t="n">
-        <v>3401931.300560741</v>
+        <v>7841931.300560742</v>
       </c>
       <c r="L78" t="n">
         <v>1</v>
@@ -13282,22 +13718,22 @@
         <v>-0</v>
       </c>
       <c r="F79" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="I79" t="n">
-        <v>1195273.159656477</v>
+        <v>2755273.159656477</v>
       </c>
       <c r="J79" t="n">
-        <v>3401931.300560741</v>
+        <v>7841931.300560742</v>
       </c>
       <c r="K79" t="n">
-        <v>3401931.300560741</v>
+        <v>7841931.300560742</v>
       </c>
       <c r="L79" t="n">
         <v>1</v>
@@ -13324,22 +13760,22 @@
         <v>-0</v>
       </c>
       <c r="F80" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="I80" t="n">
-        <v>1195273.159656477</v>
+        <v>2755273.159656477</v>
       </c>
       <c r="J80" t="n">
-        <v>3401931.300560741</v>
+        <v>7841931.300560742</v>
       </c>
       <c r="K80" t="n">
-        <v>3401931.300560741</v>
+        <v>7841931.300560742</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -13366,22 +13802,22 @@
         <v>-0</v>
       </c>
       <c r="F81" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="I81" t="n">
-        <v>1195273.159656477</v>
+        <v>2755273.159656477</v>
       </c>
       <c r="J81" t="n">
-        <v>3401931.300560741</v>
+        <v>7841931.300560742</v>
       </c>
       <c r="K81" t="n">
-        <v>3401931.300560741</v>
+        <v>7841931.300560742</v>
       </c>
       <c r="L81" t="n">
         <v>1</v>
@@ -13408,22 +13844,22 @@
         <v>-0</v>
       </c>
       <c r="F82" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="I82" t="n">
-        <v>1195273.159656477</v>
+        <v>2755273.159656477</v>
       </c>
       <c r="J82" t="n">
-        <v>3401931.300560741</v>
+        <v>7841931.300560742</v>
       </c>
       <c r="K82" t="n">
-        <v>3401931.300560741</v>
+        <v>7841931.300560742</v>
       </c>
       <c r="L82" t="n">
         <v>1</v>
@@ -13450,22 +13886,22 @@
         <v>-0</v>
       </c>
       <c r="F83" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="I83" t="n">
-        <v>1195273.159656477</v>
+        <v>2755273.159656477</v>
       </c>
       <c r="J83" t="n">
-        <v>3401931.300560741</v>
+        <v>7841931.300560742</v>
       </c>
       <c r="K83" t="n">
-        <v>3401931.300560741</v>
+        <v>7841931.300560742</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
@@ -13492,22 +13928,22 @@
         <v>-0</v>
       </c>
       <c r="F84" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="I84" t="n">
-        <v>1195273.159656477</v>
+        <v>2755273.159656477</v>
       </c>
       <c r="J84" t="n">
-        <v>3401931.300560741</v>
+        <v>7841931.300560742</v>
       </c>
       <c r="K84" t="n">
-        <v>3401931.300560741</v>
+        <v>7841931.300560742</v>
       </c>
       <c r="L84" t="n">
         <v>1</v>
@@ -13534,22 +13970,22 @@
         <v>-0</v>
       </c>
       <c r="F85" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="I85" t="n">
-        <v>1195273.159656477</v>
+        <v>2755273.159656477</v>
       </c>
       <c r="J85" t="n">
-        <v>3401931.300560741</v>
+        <v>7841931.300560742</v>
       </c>
       <c r="K85" t="n">
-        <v>3401931.300560741</v>
+        <v>7841931.300560742</v>
       </c>
       <c r="L85" t="n">
         <v>1</v>
@@ -13576,22 +14012,22 @@
         <v>-5127031.06420671</v>
       </c>
       <c r="F86" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>4597204.460217218</v>
+        <v>10597204.46021722</v>
       </c>
       <c r="I86" t="n">
-        <v>1195273.159656477</v>
+        <v>2755273.159656477</v>
       </c>
       <c r="J86" t="n">
-        <v>3401931.300560741</v>
+        <v>7841931.300560742</v>
       </c>
       <c r="K86" t="n">
-        <v>8528962.364767451</v>
+        <v>12968962.36476745</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
